--- a/data/Matriz_Seguimiento_Hallazgos.xlsx
+++ b/data/Matriz_Seguimiento_Hallazgos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Dashboard_Auditoria/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Dashboard-Auditoria/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="526" documentId="8_{B9D78422-FDFF-47F2-8818-479A70B2C122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BDE7E75-6593-42F2-93FF-C4C2C89A87CA}"/>
+  <xr:revisionPtr revIDLastSave="603" documentId="8_{B9D78422-FDFF-47F2-8818-479A70B2C122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{382B4E11-A690-47A1-9445-EA0F808FD212}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base Hallazgos SIG" sheetId="4" r:id="rId1"/>
@@ -19,10 +19,10 @@
     <sheet name="Dashboard_Comité" sheetId="2" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Base Hallazgos Aseguramiento'!$A$1:$AD$206</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base Hallazgos SIG'!$A$1:$AF$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Base Hallazgos Aseguramiento'!$A$1:$AE$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base Hallazgos SIG'!$A$1:$AG$13</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="207">
   <si>
     <t>Código Hallazgo</t>
   </si>
@@ -196,12 +196,6 @@
 5. Debilidad en la segregación de funciones.</t>
   </si>
   <si>
-    <t>Proceso / Subproceso Auditado</t>
-  </si>
-  <si>
-    <t>Mercadeo, admisiones y matrícula / Inscripción, admisión y matrícula de estudiantes nuevos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Libia Cabra / Ivonne Marin </t>
   </si>
   <si>
@@ -241,9 +235,6 @@
     <t xml:space="preserve">Estudiantes próximos a graduarse que presentaron  documentación fraudulenta, o con documentación incompleta. </t>
   </si>
   <si>
-    <t xml:space="preserve">Extensión / Gestión de la responsabilidad social </t>
-  </si>
-  <si>
     <t>Liquidación de comisiones FINCOMERCIO</t>
   </si>
   <si>
@@ -308,9 +299,6 @@
   </si>
   <si>
     <t>Contratos B2G</t>
-  </si>
-  <si>
-    <t>Mercadeo, admisiones y matrícula / Mercadeo y venta de educación para la vida</t>
   </si>
   <si>
     <t>John Jaime Marin</t>
@@ -608,12 +596,150 @@
     <t>Hecho Cumplido
 Ley 1581/2012 Arts. 3, 5, 6 (datos sensibles); Decreto 1377/2013 Art. 3</t>
   </si>
+  <si>
+    <t>Subproceso</t>
+  </si>
+  <si>
+    <t>Proceso</t>
+  </si>
+  <si>
+    <t>Mercadeo, admisiones y matrícula</t>
+  </si>
+  <si>
+    <t>Extensión</t>
+  </si>
+  <si>
+    <t>Inscripción, admisión y matrícula de estudiantes nuevos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gestión de la responsabilidad social </t>
+  </si>
+  <si>
+    <t>Mercadeo y venta de educación para la vida</t>
+  </si>
+  <si>
+    <t>Sistemas de gestión Integrados</t>
+  </si>
+  <si>
+    <t>Sistema de gestión ambiental</t>
+  </si>
+  <si>
+    <t>Sistema de gestión de calidad</t>
+  </si>
+  <si>
+    <t>Sistema de Gestión de Seguridad y Salud en el Trabajo</t>
+  </si>
+  <si>
+    <t>HSIG-1</t>
+  </si>
+  <si>
+    <t>HSIG-2</t>
+  </si>
+  <si>
+    <t>HSIG-3</t>
+  </si>
+  <si>
+    <t>HSIG-4</t>
+  </si>
+  <si>
+    <t>HSIG-5</t>
+  </si>
+  <si>
+    <t>HSIG-6</t>
+  </si>
+  <si>
+    <t>HSIG-7</t>
+  </si>
+  <si>
+    <t>HSIG-8</t>
+  </si>
+  <si>
+    <t>HSIG-9</t>
+  </si>
+  <si>
+    <t>HSIG-10</t>
+  </si>
+  <si>
+    <t>HSIG-11</t>
+  </si>
+  <si>
+    <t>HASEG-1</t>
+  </si>
+  <si>
+    <t>HASEG-2</t>
+  </si>
+  <si>
+    <t>HASEG-3</t>
+  </si>
+  <si>
+    <t>HASEG-4</t>
+  </si>
+  <si>
+    <t>HASEG-5</t>
+  </si>
+  <si>
+    <t>HASEG-6</t>
+  </si>
+  <si>
+    <t>HASEG-7</t>
+  </si>
+  <si>
+    <t>HASEG-8</t>
+  </si>
+  <si>
+    <t>HASEG-9</t>
+  </si>
+  <si>
+    <t>HASEG-10</t>
+  </si>
+  <si>
+    <t>HASEG-11</t>
+  </si>
+  <si>
+    <t>HASEG-12</t>
+  </si>
+  <si>
+    <t>HASEG-13</t>
+  </si>
+  <si>
+    <t>HASEG-14</t>
+  </si>
+  <si>
+    <t>HASEG-15</t>
+  </si>
+  <si>
+    <t>HASEG-16</t>
+  </si>
+  <si>
+    <t>HASEG-17</t>
+  </si>
+  <si>
+    <t>HASEG-18</t>
+  </si>
+  <si>
+    <t>HASEG-19</t>
+  </si>
+  <si>
+    <t>HASEG-20</t>
+  </si>
+  <si>
+    <t>HASEG-21</t>
+  </si>
+  <si>
+    <t>HASEG-22</t>
+  </si>
+  <si>
+    <t>HASEG-23</t>
+  </si>
+  <si>
+    <t>HASEG-24</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -652,6 +778,12 @@
       <color rgb="FF002060"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -801,20 +933,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="17" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -843,7 +975,9 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{807F978E-0166-4674-A7F2-10D8FC7F1DF6}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1140,27 +1274,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{220792B3-42C8-4F5F-876D-A137B68C9789}">
-  <dimension ref="A1:AF205"/>
+  <dimension ref="A1:AG205"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" style="9" customWidth="1"/>
     <col min="2" max="2" width="13.88671875" style="9" customWidth="1"/>
     <col min="3" max="3" width="16.88671875" style="13" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" style="9" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="16.21875" style="9" customWidth="1"/>
-    <col min="7" max="7" width="25" style="9" customWidth="1"/>
-    <col min="8" max="8" width="64.33203125" style="15" customWidth="1"/>
-    <col min="9" max="9" width="22" style="9" customWidth="1"/>
-    <col min="10" max="10" width="47.33203125" style="9" customWidth="1"/>
-    <col min="11" max="12" width="22" style="13" customWidth="1"/>
-    <col min="13" max="13" width="22" style="9" customWidth="1"/>
-    <col min="14" max="14" width="29.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="32" width="22" style="9" customWidth="1"/>
-    <col min="33" max="16384" width="8.77734375" style="9"/>
+    <col min="4" max="5" width="14.88671875" style="9" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="9" customWidth="1"/>
+    <col min="7" max="7" width="16.21875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="25" style="9" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="15" customWidth="1"/>
+    <col min="10" max="10" width="22" style="9" customWidth="1"/>
+    <col min="11" max="11" width="47.33203125" style="9" customWidth="1"/>
+    <col min="12" max="13" width="22" style="13" customWidth="1"/>
+    <col min="14" max="14" width="22" style="9" customWidth="1"/>
+    <col min="15" max="15" width="29.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="33" width="22" style="9" customWidth="1"/>
+    <col min="34" max="16384" width="8.77734375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1168,128 +1302,135 @@
         <v>2</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>46</v>
+        <v>162</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="I1" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="M1" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AG1" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:32" s="7" customFormat="1" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
+    <row r="2" spans="1:33" s="7" customFormat="1" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>172</v>
+      </c>
       <c r="B2" s="6">
         <v>45855</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>93</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="5">
+        <v>88</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J2" s="5"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="5">
         <v>426</v>
       </c>
-      <c r="L2" s="16">
+      <c r="M2" s="16">
         <v>0.4</v>
       </c>
-      <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
@@ -1302,50 +1443,55 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
       <c r="Y2" s="5"/>
-      <c r="Z2" s="5" t="s">
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AB2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AB2" s="5"/>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
       <c r="AE2" s="5"/>
       <c r="AF2" s="5"/>
-    </row>
-    <row r="3" spans="1:32" s="7" customFormat="1" ht="211.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
+      <c r="AG2" s="5"/>
+    </row>
+    <row r="3" spans="1:33" s="7" customFormat="1" ht="211.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>173</v>
+      </c>
       <c r="B3" s="6">
         <v>45855</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>115</v>
+        <v>92</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>102</v>
+        <v>111</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="5">
+        <v>99</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="5">
         <v>429</v>
       </c>
-      <c r="L3" s="18">
+      <c r="M3" s="18">
         <v>0.88890000000000002</v>
       </c>
-      <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
@@ -1365,39 +1511,44 @@
       <c r="AD3" s="5"/>
       <c r="AE3" s="5"/>
       <c r="AF3" s="5"/>
-    </row>
-    <row r="4" spans="1:32" s="11" customFormat="1" ht="211.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
+      <c r="AG3" s="5"/>
+    </row>
+    <row r="4" spans="1:33" s="11" customFormat="1" ht="211.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>174</v>
+      </c>
       <c r="B4" s="6">
         <v>45855</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="5">
+      <c r="K4" s="3"/>
+      <c r="L4" s="5">
         <v>431</v>
       </c>
-      <c r="L4" s="16">
+      <c r="M4" s="16">
         <v>1</v>
       </c>
-      <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
@@ -1417,39 +1568,44 @@
       <c r="AD4" s="3"/>
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
-    </row>
-    <row r="5" spans="1:32" s="11" customFormat="1" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
+      <c r="AG4" s="3"/>
+    </row>
+    <row r="5" spans="1:33" s="11" customFormat="1" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>175</v>
+      </c>
       <c r="B5" s="6">
         <v>45855</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>117</v>
+        <v>92</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="I5" s="3"/>
+        <v>102</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="5">
+      <c r="K5" s="3"/>
+      <c r="L5" s="5">
         <v>427</v>
       </c>
-      <c r="L5" s="16">
+      <c r="M5" s="16">
         <v>1</v>
       </c>
-      <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
@@ -1469,39 +1625,44 @@
       <c r="AD5" s="3"/>
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
-    </row>
-    <row r="6" spans="1:32" s="11" customFormat="1" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
+      <c r="AG5" s="3"/>
+    </row>
+    <row r="6" spans="1:33" s="11" customFormat="1" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>176</v>
+      </c>
       <c r="B6" s="6">
         <v>45855</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="I6" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="5">
+      <c r="K6" s="3"/>
+      <c r="L6" s="5">
         <v>430</v>
       </c>
-      <c r="L6" s="16">
+      <c r="M6" s="16">
         <v>1</v>
       </c>
-      <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
@@ -1521,39 +1682,44 @@
       <c r="AD6" s="3"/>
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
-    </row>
-    <row r="7" spans="1:32" s="11" customFormat="1" ht="198" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
+      <c r="AG6" s="3"/>
+    </row>
+    <row r="7" spans="1:33" s="11" customFormat="1" ht="198" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>177</v>
+      </c>
       <c r="B7" s="6">
         <v>45855</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="I7" s="3"/>
+        <v>108</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="5">
+      <c r="K7" s="3"/>
+      <c r="L7" s="5">
         <v>428</v>
       </c>
-      <c r="L7" s="16">
+      <c r="M7" s="16">
         <v>1</v>
       </c>
-      <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -1573,39 +1739,44 @@
       <c r="AD7" s="3"/>
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
-    </row>
-    <row r="8" spans="1:32" s="11" customFormat="1" ht="66" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
+      <c r="AG7" s="3"/>
+    </row>
+    <row r="8" spans="1:33" s="11" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>178</v>
+      </c>
       <c r="B8" s="6">
         <v>45962</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>142</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="I8" s="3"/>
+        <v>128</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="J8" s="3"/>
-      <c r="K8" s="5">
+      <c r="K8" s="3"/>
+      <c r="L8" s="5">
         <v>452</v>
       </c>
-      <c r="L8" s="18">
+      <c r="M8" s="18">
         <v>0</v>
       </c>
-      <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
@@ -1625,39 +1796,44 @@
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
       <c r="AF8" s="3"/>
-    </row>
-    <row r="9" spans="1:32" s="11" customFormat="1" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
+      <c r="AG8" s="3"/>
+    </row>
+    <row r="9" spans="1:33" s="11" customFormat="1" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>179</v>
+      </c>
       <c r="B9" s="6">
         <v>45962</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>147</v>
+        <v>114</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="I9" s="3"/>
+        <v>115</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="J9" s="3"/>
-      <c r="K9" s="5">
+      <c r="K9" s="3"/>
+      <c r="L9" s="5">
         <v>449</v>
       </c>
-      <c r="L9" s="18">
+      <c r="M9" s="18">
         <v>7.1400000000000005E-2</v>
       </c>
-      <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -1677,39 +1853,44 @@
       <c r="AD9" s="3"/>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
-    </row>
-    <row r="10" spans="1:32" s="11" customFormat="1" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
+      <c r="AG9" s="3"/>
+    </row>
+    <row r="10" spans="1:33" s="11" customFormat="1" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>180</v>
+      </c>
       <c r="B10" s="6">
         <v>45962</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="5">
+      <c r="K10" s="3"/>
+      <c r="L10" s="5">
         <v>450</v>
       </c>
-      <c r="L10" s="18">
+      <c r="M10" s="18">
         <v>0.12</v>
       </c>
-      <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1729,39 +1910,44 @@
       <c r="AD10" s="3"/>
       <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
-    </row>
-    <row r="11" spans="1:32" s="11" customFormat="1" ht="43.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24"/>
-      <c r="B11" s="27">
+      <c r="AG10" s="3"/>
+    </row>
+    <row r="11" spans="1:33" s="11" customFormat="1" ht="43.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11" s="24">
         <v>45962</v>
       </c>
-      <c r="C11" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="E11" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="G11" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="H11" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="I11" s="3"/>
+      <c r="C11" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>136</v>
+      </c>
       <c r="J11" s="3"/>
-      <c r="K11" s="5">
+      <c r="K11" s="3"/>
+      <c r="L11" s="5">
         <v>454</v>
       </c>
-      <c r="L11" s="18">
+      <c r="M11" s="18">
         <v>0</v>
       </c>
-      <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1781,40 +1967,45 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" s="11" customFormat="1" ht="43.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" s="11" customFormat="1" ht="43.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B12" s="24">
         <v>45962</v>
       </c>
-      <c r="C12" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="I12" s="3"/>
+      <c r="C12" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="I12" s="25" t="s">
+        <v>136</v>
+      </c>
       <c r="J12" s="3"/>
-      <c r="K12" s="5">
+      <c r="K12" s="3"/>
+      <c r="L12" s="5">
         <v>451</v>
       </c>
-      <c r="L12" s="18">
+      <c r="M12" s="18">
         <v>0.66669999999999996</v>
       </c>
-      <c r="M12" s="17"/>
-      <c r="N12" s="3"/>
+      <c r="N12" s="17"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -1833,39 +2024,44 @@
       <c r="AD12" s="3"/>
       <c r="AE12" s="3"/>
       <c r="AF12" s="3"/>
-    </row>
-    <row r="13" spans="1:32" s="11" customFormat="1" ht="66" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
+      <c r="AG12" s="3"/>
+    </row>
+    <row r="13" spans="1:33" s="11" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>182</v>
+      </c>
       <c r="B13" s="6">
         <v>45962</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>97</v>
+        <v>169</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="I13" s="3"/>
+        <v>138</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="J13" s="3"/>
-      <c r="K13" s="5">
+      <c r="K13" s="3"/>
+      <c r="L13" s="5">
         <v>453</v>
       </c>
-      <c r="L13" s="18">
+      <c r="M13" s="18">
         <v>0.11</v>
       </c>
-      <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -1885,8 +2081,9 @@
       <c r="AD13" s="3"/>
       <c r="AE13" s="3"/>
       <c r="AF13" s="3"/>
-    </row>
-    <row r="14" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG13" s="3"/>
+    </row>
+    <row r="14" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="6"/>
       <c r="C14" s="5"/>
@@ -1897,9 +2094,9 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="5"/>
+      <c r="K14" s="3"/>
       <c r="L14" s="5"/>
-      <c r="M14" s="3"/>
+      <c r="M14" s="5"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -1919,8 +2116,9 @@
       <c r="AD14" s="3"/>
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
-    </row>
-    <row r="15" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG14" s="3"/>
+    </row>
+    <row r="15" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="6"/>
       <c r="C15" s="5"/>
@@ -1931,9 +2129,9 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="5"/>
+      <c r="K15" s="3"/>
       <c r="L15" s="5"/>
-      <c r="M15" s="3"/>
+      <c r="M15" s="5"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -1953,8 +2151,9 @@
       <c r="AD15" s="3"/>
       <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
-    </row>
-    <row r="16" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG15" s="3"/>
+    </row>
+    <row r="16" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="6"/>
       <c r="C16" s="5"/>
@@ -1965,9 +2164,9 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="5"/>
+      <c r="K16" s="3"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="3"/>
+      <c r="M16" s="5"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -1987,8 +2186,9 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="6"/>
       <c r="C17" s="5"/>
@@ -1999,9 +2199,9 @@
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="5"/>
+      <c r="K17" s="3"/>
       <c r="L17" s="5"/>
-      <c r="M17" s="3"/>
+      <c r="M17" s="5"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -2021,8 +2221,9 @@
       <c r="AD17" s="3"/>
       <c r="AE17" s="3"/>
       <c r="AF17" s="3"/>
-    </row>
-    <row r="18" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG17" s="3"/>
+    </row>
+    <row r="18" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="6"/>
       <c r="C18" s="5"/>
@@ -2033,9 +2234,9 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="5"/>
+      <c r="K18" s="3"/>
       <c r="L18" s="5"/>
-      <c r="M18" s="3"/>
+      <c r="M18" s="5"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -2055,8 +2256,9 @@
       <c r="AD18" s="3"/>
       <c r="AE18" s="3"/>
       <c r="AF18" s="3"/>
-    </row>
-    <row r="19" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG18" s="3"/>
+    </row>
+    <row r="19" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="6"/>
       <c r="C19" s="5"/>
@@ -2067,9 +2269,9 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="5"/>
+      <c r="K19" s="3"/>
       <c r="L19" s="5"/>
-      <c r="M19" s="3"/>
+      <c r="M19" s="5"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -2089,8 +2291,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="6"/>
       <c r="C20" s="5"/>
@@ -2101,9 +2304,9 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="5"/>
+      <c r="K20" s="3"/>
       <c r="L20" s="5"/>
-      <c r="M20" s="3"/>
+      <c r="M20" s="5"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -2123,8 +2326,9 @@
       <c r="AD20" s="3"/>
       <c r="AE20" s="3"/>
       <c r="AF20" s="3"/>
-    </row>
-    <row r="21" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG20" s="3"/>
+    </row>
+    <row r="21" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="6"/>
       <c r="C21" s="5"/>
@@ -2135,9 +2339,9 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="5"/>
+      <c r="K21" s="3"/>
       <c r="L21" s="5"/>
-      <c r="M21" s="3"/>
+      <c r="M21" s="5"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -2157,8 +2361,9 @@
       <c r="AD21" s="3"/>
       <c r="AE21" s="3"/>
       <c r="AF21" s="3"/>
-    </row>
-    <row r="22" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG21" s="3"/>
+    </row>
+    <row r="22" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="6"/>
       <c r="C22" s="5"/>
@@ -2169,9 +2374,9 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
-      <c r="K22" s="5"/>
+      <c r="K22" s="3"/>
       <c r="L22" s="5"/>
-      <c r="M22" s="3"/>
+      <c r="M22" s="5"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -2191,8 +2396,9 @@
       <c r="AD22" s="3"/>
       <c r="AE22" s="3"/>
       <c r="AF22" s="3"/>
-    </row>
-    <row r="23" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG22" s="3"/>
+    </row>
+    <row r="23" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="6"/>
       <c r="C23" s="5"/>
@@ -2203,9 +2409,9 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="5"/>
+      <c r="K23" s="3"/>
       <c r="L23" s="5"/>
-      <c r="M23" s="3"/>
+      <c r="M23" s="5"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -2225,8 +2431,9 @@
       <c r="AD23" s="3"/>
       <c r="AE23" s="3"/>
       <c r="AF23" s="3"/>
-    </row>
-    <row r="24" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG23" s="3"/>
+    </row>
+    <row r="24" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="6"/>
       <c r="C24" s="5"/>
@@ -2237,9 +2444,9 @@
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
-      <c r="K24" s="5"/>
+      <c r="K24" s="3"/>
       <c r="L24" s="5"/>
-      <c r="M24" s="3"/>
+      <c r="M24" s="5"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -2259,8 +2466,9 @@
       <c r="AD24" s="3"/>
       <c r="AE24" s="3"/>
       <c r="AF24" s="3"/>
-    </row>
-    <row r="25" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG24" s="3"/>
+    </row>
+    <row r="25" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="5"/>
@@ -2271,9 +2479,9 @@
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
-      <c r="K25" s="5"/>
+      <c r="K25" s="3"/>
       <c r="L25" s="5"/>
-      <c r="M25" s="3"/>
+      <c r="M25" s="5"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -2293,8 +2501,9 @@
       <c r="AD25" s="3"/>
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
-    </row>
-    <row r="26" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG25" s="3"/>
+    </row>
+    <row r="26" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="5"/>
@@ -2305,19 +2514,19 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
-      <c r="K26" s="5"/>
+      <c r="K26" s="3"/>
       <c r="L26" s="5"/>
-      <c r="M26" s="3"/>
+      <c r="M26" s="5"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
-      <c r="S26" s="3" t="str">
-        <f t="shared" ref="S26:S70" ca="1" si="0">IF(AND(P26&lt;TODAY(),S26&lt;&gt;"Cerrado"),"Vencido",S26)</f>
-        <v/>
-      </c>
-      <c r="T26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3" t="str">
+        <f t="shared" ref="T26:T70" ca="1" si="0">IF(AND(Q26&lt;TODAY(),T26&lt;&gt;"Cerrado"),"Vencido",T26)</f>
+        <v/>
+      </c>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -2330,8 +2539,9 @@
       <c r="AD26" s="3"/>
       <c r="AE26" s="3"/>
       <c r="AF26" s="3"/>
-    </row>
-    <row r="27" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG26" s="3"/>
+    </row>
+    <row r="27" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="5"/>
@@ -2342,19 +2552,19 @@
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
-      <c r="K27" s="5"/>
+      <c r="K27" s="3"/>
       <c r="L27" s="5"/>
-      <c r="M27" s="3"/>
+      <c r="M27" s="5"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
-      <c r="S27" s="3" t="str">
+      <c r="S27" s="3"/>
+      <c r="T27" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T27" s="3"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -2367,8 +2577,9 @@
       <c r="AD27" s="3"/>
       <c r="AE27" s="3"/>
       <c r="AF27" s="3"/>
-    </row>
-    <row r="28" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG27" s="3"/>
+    </row>
+    <row r="28" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="5"/>
@@ -2379,19 +2590,19 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="5"/>
+      <c r="K28" s="3"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="3"/>
+      <c r="M28" s="5"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
-      <c r="S28" s="3" t="str">
+      <c r="S28" s="3"/>
+      <c r="T28" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -2404,8 +2615,9 @@
       <c r="AD28" s="3"/>
       <c r="AE28" s="3"/>
       <c r="AF28" s="3"/>
-    </row>
-    <row r="29" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG28" s="3"/>
+    </row>
+    <row r="29" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="5"/>
@@ -2416,19 +2628,19 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
-      <c r="K29" s="5"/>
+      <c r="K29" s="3"/>
       <c r="L29" s="5"/>
-      <c r="M29" s="3"/>
+      <c r="M29" s="5"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
-      <c r="S29" s="3" t="str">
+      <c r="S29" s="3"/>
+      <c r="T29" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T29" s="3"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -2441,8 +2653,9 @@
       <c r="AD29" s="3"/>
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
-    </row>
-    <row r="30" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG29" s="3"/>
+    </row>
+    <row r="30" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="5"/>
@@ -2453,19 +2666,19 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="5"/>
+      <c r="K30" s="3"/>
       <c r="L30" s="5"/>
-      <c r="M30" s="3"/>
+      <c r="M30" s="5"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
-      <c r="S30" s="3" t="str">
+      <c r="S30" s="3"/>
+      <c r="T30" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -2478,8 +2691,9 @@
       <c r="AD30" s="3"/>
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
-    </row>
-    <row r="31" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG30" s="3"/>
+    </row>
+    <row r="31" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="5"/>
@@ -2490,19 +2704,19 @@
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
-      <c r="K31" s="5"/>
+      <c r="K31" s="3"/>
       <c r="L31" s="5"/>
-      <c r="M31" s="3"/>
+      <c r="M31" s="5"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
-      <c r="S31" s="3" t="str">
+      <c r="S31" s="3"/>
+      <c r="T31" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T31" s="3"/>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -2515,8 +2729,9 @@
       <c r="AD31" s="3"/>
       <c r="AE31" s="3"/>
       <c r="AF31" s="3"/>
-    </row>
-    <row r="32" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG31" s="3"/>
+    </row>
+    <row r="32" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="5"/>
@@ -2527,19 +2742,19 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
-      <c r="K32" s="5"/>
+      <c r="K32" s="3"/>
       <c r="L32" s="5"/>
-      <c r="M32" s="3"/>
+      <c r="M32" s="5"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
-      <c r="S32" s="3" t="str">
+      <c r="S32" s="3"/>
+      <c r="T32" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -2552,8 +2767,9 @@
       <c r="AD32" s="3"/>
       <c r="AE32" s="3"/>
       <c r="AF32" s="3"/>
-    </row>
-    <row r="33" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG32" s="3"/>
+    </row>
+    <row r="33" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="5"/>
@@ -2564,19 +2780,19 @@
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="5"/>
+      <c r="K33" s="3"/>
       <c r="L33" s="5"/>
-      <c r="M33" s="3"/>
+      <c r="M33" s="5"/>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
-      <c r="S33" s="3" t="str">
+      <c r="S33" s="3"/>
+      <c r="T33" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -2589,8 +2805,9 @@
       <c r="AD33" s="3"/>
       <c r="AE33" s="3"/>
       <c r="AF33" s="3"/>
-    </row>
-    <row r="34" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG33" s="3"/>
+    </row>
+    <row r="34" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="5"/>
@@ -2601,19 +2818,19 @@
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="5"/>
+      <c r="K34" s="3"/>
       <c r="L34" s="5"/>
-      <c r="M34" s="3"/>
+      <c r="M34" s="5"/>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
-      <c r="S34" s="3" t="str">
+      <c r="S34" s="3"/>
+      <c r="T34" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -2626,8 +2843,9 @@
       <c r="AD34" s="3"/>
       <c r="AE34" s="3"/>
       <c r="AF34" s="3"/>
-    </row>
-    <row r="35" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG34" s="3"/>
+    </row>
+    <row r="35" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="5"/>
@@ -2638,19 +2856,19 @@
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="5"/>
+      <c r="K35" s="3"/>
       <c r="L35" s="5"/>
-      <c r="M35" s="3"/>
+      <c r="M35" s="5"/>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
-      <c r="S35" s="3" t="str">
+      <c r="S35" s="3"/>
+      <c r="T35" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T35" s="3"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -2663,8 +2881,9 @@
       <c r="AD35" s="3"/>
       <c r="AE35" s="3"/>
       <c r="AF35" s="3"/>
-    </row>
-    <row r="36" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG35" s="3"/>
+    </row>
+    <row r="36" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="5"/>
@@ -2675,19 +2894,19 @@
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="5"/>
+      <c r="K36" s="3"/>
       <c r="L36" s="5"/>
-      <c r="M36" s="3"/>
+      <c r="M36" s="5"/>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
-      <c r="S36" s="3" t="str">
+      <c r="S36" s="3"/>
+      <c r="T36" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -2700,8 +2919,9 @@
       <c r="AD36" s="3"/>
       <c r="AE36" s="3"/>
       <c r="AF36" s="3"/>
-    </row>
-    <row r="37" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG36" s="3"/>
+    </row>
+    <row r="37" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="5"/>
@@ -2712,19 +2932,19 @@
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="5"/>
+      <c r="K37" s="3"/>
       <c r="L37" s="5"/>
-      <c r="M37" s="3"/>
+      <c r="M37" s="5"/>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
-      <c r="S37" s="3" t="str">
+      <c r="S37" s="3"/>
+      <c r="T37" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T37" s="3"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
@@ -2737,8 +2957,9 @@
       <c r="AD37" s="3"/>
       <c r="AE37" s="3"/>
       <c r="AF37" s="3"/>
-    </row>
-    <row r="38" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG37" s="3"/>
+    </row>
+    <row r="38" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="5"/>
@@ -2749,19 +2970,19 @@
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="5"/>
+      <c r="K38" s="3"/>
       <c r="L38" s="5"/>
-      <c r="M38" s="3"/>
+      <c r="M38" s="5"/>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
-      <c r="S38" s="3" t="str">
+      <c r="S38" s="3"/>
+      <c r="T38" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
@@ -2774,8 +2995,9 @@
       <c r="AD38" s="3"/>
       <c r="AE38" s="3"/>
       <c r="AF38" s="3"/>
-    </row>
-    <row r="39" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG38" s="3"/>
+    </row>
+    <row r="39" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="5"/>
@@ -2786,19 +3008,19 @@
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="5"/>
+      <c r="K39" s="3"/>
       <c r="L39" s="5"/>
-      <c r="M39" s="3"/>
+      <c r="M39" s="5"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-      <c r="S39" s="3" t="str">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -2811,8 +3033,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="5"/>
@@ -2823,19 +3046,19 @@
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="5"/>
+      <c r="K40" s="3"/>
       <c r="L40" s="5"/>
-      <c r="M40" s="3"/>
+      <c r="M40" s="5"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-      <c r="S40" s="3" t="str">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -2848,8 +3071,9 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="5"/>
@@ -2860,19 +3084,19 @@
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="5"/>
+      <c r="K41" s="3"/>
       <c r="L41" s="5"/>
-      <c r="M41" s="3"/>
+      <c r="M41" s="5"/>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
-      <c r="S41" s="3" t="str">
+      <c r="S41" s="3"/>
+      <c r="T41" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T41" s="3"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -2885,8 +3109,9 @@
       <c r="AD41" s="3"/>
       <c r="AE41" s="3"/>
       <c r="AF41" s="3"/>
-    </row>
-    <row r="42" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG41" s="3"/>
+    </row>
+    <row r="42" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="5"/>
@@ -2897,19 +3122,19 @@
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="5"/>
+      <c r="K42" s="3"/>
       <c r="L42" s="5"/>
-      <c r="M42" s="3"/>
+      <c r="M42" s="5"/>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
       <c r="R42" s="3"/>
-      <c r="S42" s="3" t="str">
+      <c r="S42" s="3"/>
+      <c r="T42" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
@@ -2922,8 +3147,9 @@
       <c r="AD42" s="3"/>
       <c r="AE42" s="3"/>
       <c r="AF42" s="3"/>
-    </row>
-    <row r="43" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG42" s="3"/>
+    </row>
+    <row r="43" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="5"/>
@@ -2934,19 +3160,19 @@
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="5"/>
+      <c r="K43" s="3"/>
       <c r="L43" s="5"/>
-      <c r="M43" s="3"/>
+      <c r="M43" s="5"/>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
-      <c r="S43" s="3" t="str">
+      <c r="S43" s="3"/>
+      <c r="T43" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T43" s="3"/>
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
@@ -2959,8 +3185,9 @@
       <c r="AD43" s="3"/>
       <c r="AE43" s="3"/>
       <c r="AF43" s="3"/>
-    </row>
-    <row r="44" spans="1:32" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AG43" s="3"/>
+    </row>
+    <row r="44" spans="1:33" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="5"/>
@@ -2971,19 +3198,19 @@
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="5"/>
+      <c r="K44" s="3"/>
       <c r="L44" s="5"/>
-      <c r="M44" s="3"/>
+      <c r="M44" s="5"/>
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
-      <c r="S44" s="3" t="str">
+      <c r="S44" s="3"/>
+      <c r="T44" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -2996,8 +3223,9 @@
       <c r="AD44" s="3"/>
       <c r="AE44" s="3"/>
       <c r="AF44" s="3"/>
-    </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG44" s="3"/>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="12"/>
@@ -3005,22 +3233,22 @@
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="14"/>
       <c r="J45" s="8"/>
-      <c r="K45" s="12"/>
+      <c r="K45" s="8"/>
       <c r="L45" s="12"/>
-      <c r="M45" s="8"/>
+      <c r="M45" s="12"/>
       <c r="N45" s="8"/>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
       <c r="Q45" s="8"/>
       <c r="R45" s="8"/>
-      <c r="S45" s="8" t="str">
+      <c r="S45" s="8"/>
+      <c r="T45" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T45" s="8"/>
       <c r="U45" s="8"/>
       <c r="V45" s="8"/>
       <c r="W45" s="8"/>
@@ -3033,8 +3261,9 @@
       <c r="AD45" s="8"/>
       <c r="AE45" s="8"/>
       <c r="AF45" s="8"/>
-    </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG45" s="8"/>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="12"/>
@@ -3042,22 +3271,22 @@
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="14"/>
       <c r="J46" s="8"/>
-      <c r="K46" s="12"/>
+      <c r="K46" s="8"/>
       <c r="L46" s="12"/>
-      <c r="M46" s="8"/>
+      <c r="M46" s="12"/>
       <c r="N46" s="8"/>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
       <c r="Q46" s="8"/>
       <c r="R46" s="8"/>
-      <c r="S46" s="8" t="str">
+      <c r="S46" s="8"/>
+      <c r="T46" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T46" s="8"/>
       <c r="U46" s="8"/>
       <c r="V46" s="8"/>
       <c r="W46" s="8"/>
@@ -3070,8 +3299,9 @@
       <c r="AD46" s="8"/>
       <c r="AE46" s="8"/>
       <c r="AF46" s="8"/>
-    </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG46" s="8"/>
+    </row>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="12"/>
@@ -3079,22 +3309,22 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="14"/>
       <c r="J47" s="8"/>
-      <c r="K47" s="12"/>
+      <c r="K47" s="8"/>
       <c r="L47" s="12"/>
-      <c r="M47" s="8"/>
+      <c r="M47" s="12"/>
       <c r="N47" s="8"/>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
       <c r="Q47" s="8"/>
       <c r="R47" s="8"/>
-      <c r="S47" s="8" t="str">
+      <c r="S47" s="8"/>
+      <c r="T47" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T47" s="8"/>
       <c r="U47" s="8"/>
       <c r="V47" s="8"/>
       <c r="W47" s="8"/>
@@ -3107,8 +3337,9 @@
       <c r="AD47" s="8"/>
       <c r="AE47" s="8"/>
       <c r="AF47" s="8"/>
-    </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG47" s="8"/>
+    </row>
+    <row r="48" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="12"/>
@@ -3116,22 +3347,22 @@
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="14"/>
       <c r="J48" s="8"/>
-      <c r="K48" s="12"/>
+      <c r="K48" s="8"/>
       <c r="L48" s="12"/>
-      <c r="M48" s="8"/>
+      <c r="M48" s="12"/>
       <c r="N48" s="8"/>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
       <c r="Q48" s="8"/>
       <c r="R48" s="8"/>
-      <c r="S48" s="8" t="str">
+      <c r="S48" s="8"/>
+      <c r="T48" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T48" s="8"/>
       <c r="U48" s="8"/>
       <c r="V48" s="8"/>
       <c r="W48" s="8"/>
@@ -3144,8 +3375,9 @@
       <c r="AD48" s="8"/>
       <c r="AE48" s="8"/>
       <c r="AF48" s="8"/>
-    </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG48" s="8"/>
+    </row>
+    <row r="49" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="12"/>
@@ -3153,22 +3385,22 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="14"/>
       <c r="J49" s="8"/>
-      <c r="K49" s="12"/>
+      <c r="K49" s="8"/>
       <c r="L49" s="12"/>
-      <c r="M49" s="8"/>
+      <c r="M49" s="12"/>
       <c r="N49" s="8"/>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
       <c r="Q49" s="8"/>
       <c r="R49" s="8"/>
-      <c r="S49" s="8" t="str">
+      <c r="S49" s="8"/>
+      <c r="T49" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T49" s="8"/>
       <c r="U49" s="8"/>
       <c r="V49" s="8"/>
       <c r="W49" s="8"/>
@@ -3181,8 +3413,9 @@
       <c r="AD49" s="8"/>
       <c r="AE49" s="8"/>
       <c r="AF49" s="8"/>
-    </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG49" s="8"/>
+    </row>
+    <row r="50" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="12"/>
@@ -3190,22 +3423,22 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="14"/>
       <c r="J50" s="8"/>
-      <c r="K50" s="12"/>
+      <c r="K50" s="8"/>
       <c r="L50" s="12"/>
-      <c r="M50" s="8"/>
+      <c r="M50" s="12"/>
       <c r="N50" s="8"/>
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
       <c r="Q50" s="8"/>
       <c r="R50" s="8"/>
-      <c r="S50" s="8" t="str">
+      <c r="S50" s="8"/>
+      <c r="T50" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T50" s="8"/>
       <c r="U50" s="8"/>
       <c r="V50" s="8"/>
       <c r="W50" s="8"/>
@@ -3218,8 +3451,9 @@
       <c r="AD50" s="8"/>
       <c r="AE50" s="8"/>
       <c r="AF50" s="8"/>
-    </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG50" s="8"/>
+    </row>
+    <row r="51" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="12"/>
@@ -3227,22 +3461,22 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="14"/>
       <c r="J51" s="8"/>
-      <c r="K51" s="12"/>
+      <c r="K51" s="8"/>
       <c r="L51" s="12"/>
-      <c r="M51" s="8"/>
+      <c r="M51" s="12"/>
       <c r="N51" s="8"/>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
       <c r="Q51" s="8"/>
       <c r="R51" s="8"/>
-      <c r="S51" s="8" t="str">
+      <c r="S51" s="8"/>
+      <c r="T51" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T51" s="8"/>
       <c r="U51" s="8"/>
       <c r="V51" s="8"/>
       <c r="W51" s="8"/>
@@ -3255,8 +3489,9 @@
       <c r="AD51" s="8"/>
       <c r="AE51" s="8"/>
       <c r="AF51" s="8"/>
-    </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG51" s="8"/>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="12"/>
@@ -3264,22 +3499,22 @@
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="14"/>
       <c r="J52" s="8"/>
-      <c r="K52" s="12"/>
+      <c r="K52" s="8"/>
       <c r="L52" s="12"/>
-      <c r="M52" s="8"/>
+      <c r="M52" s="12"/>
       <c r="N52" s="8"/>
       <c r="O52" s="8"/>
       <c r="P52" s="8"/>
       <c r="Q52" s="8"/>
       <c r="R52" s="8"/>
-      <c r="S52" s="8" t="str">
+      <c r="S52" s="8"/>
+      <c r="T52" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T52" s="8"/>
       <c r="U52" s="8"/>
       <c r="V52" s="8"/>
       <c r="W52" s="8"/>
@@ -3292,8 +3527,9 @@
       <c r="AD52" s="8"/>
       <c r="AE52" s="8"/>
       <c r="AF52" s="8"/>
-    </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG52" s="8"/>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="12"/>
@@ -3301,22 +3537,22 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="14"/>
       <c r="J53" s="8"/>
-      <c r="K53" s="12"/>
+      <c r="K53" s="8"/>
       <c r="L53" s="12"/>
-      <c r="M53" s="8"/>
+      <c r="M53" s="12"/>
       <c r="N53" s="8"/>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
       <c r="Q53" s="8"/>
       <c r="R53" s="8"/>
-      <c r="S53" s="8" t="str">
+      <c r="S53" s="8"/>
+      <c r="T53" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T53" s="8"/>
       <c r="U53" s="8"/>
       <c r="V53" s="8"/>
       <c r="W53" s="8"/>
@@ -3329,8 +3565,9 @@
       <c r="AD53" s="8"/>
       <c r="AE53" s="8"/>
       <c r="AF53" s="8"/>
-    </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG53" s="8"/>
+    </row>
+    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="12"/>
@@ -3338,22 +3575,22 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="14"/>
       <c r="J54" s="8"/>
-      <c r="K54" s="12"/>
+      <c r="K54" s="8"/>
       <c r="L54" s="12"/>
-      <c r="M54" s="8"/>
+      <c r="M54" s="12"/>
       <c r="N54" s="8"/>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
       <c r="Q54" s="8"/>
       <c r="R54" s="8"/>
-      <c r="S54" s="8" t="str">
+      <c r="S54" s="8"/>
+      <c r="T54" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T54" s="8"/>
       <c r="U54" s="8"/>
       <c r="V54" s="8"/>
       <c r="W54" s="8"/>
@@ -3366,8 +3603,9 @@
       <c r="AD54" s="8"/>
       <c r="AE54" s="8"/>
       <c r="AF54" s="8"/>
-    </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG54" s="8"/>
+    </row>
+    <row r="55" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="12"/>
@@ -3375,22 +3613,22 @@
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="14"/>
       <c r="J55" s="8"/>
-      <c r="K55" s="12"/>
+      <c r="K55" s="8"/>
       <c r="L55" s="12"/>
-      <c r="M55" s="8"/>
+      <c r="M55" s="12"/>
       <c r="N55" s="8"/>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
       <c r="Q55" s="8"/>
       <c r="R55" s="8"/>
-      <c r="S55" s="8" t="str">
+      <c r="S55" s="8"/>
+      <c r="T55" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T55" s="8"/>
       <c r="U55" s="8"/>
       <c r="V55" s="8"/>
       <c r="W55" s="8"/>
@@ -3403,8 +3641,9 @@
       <c r="AD55" s="8"/>
       <c r="AE55" s="8"/>
       <c r="AF55" s="8"/>
-    </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG55" s="8"/>
+    </row>
+    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="12"/>
@@ -3412,22 +3651,22 @@
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="14"/>
       <c r="J56" s="8"/>
-      <c r="K56" s="12"/>
+      <c r="K56" s="8"/>
       <c r="L56" s="12"/>
-      <c r="M56" s="8"/>
+      <c r="M56" s="12"/>
       <c r="N56" s="8"/>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
       <c r="Q56" s="8"/>
       <c r="R56" s="8"/>
-      <c r="S56" s="8" t="str">
+      <c r="S56" s="8"/>
+      <c r="T56" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T56" s="8"/>
       <c r="U56" s="8"/>
       <c r="V56" s="8"/>
       <c r="W56" s="8"/>
@@ -3440,8 +3679,9 @@
       <c r="AD56" s="8"/>
       <c r="AE56" s="8"/>
       <c r="AF56" s="8"/>
-    </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG56" s="8"/>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="12"/>
@@ -3449,22 +3689,22 @@
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="14"/>
       <c r="J57" s="8"/>
-      <c r="K57" s="12"/>
+      <c r="K57" s="8"/>
       <c r="L57" s="12"/>
-      <c r="M57" s="8"/>
+      <c r="M57" s="12"/>
       <c r="N57" s="8"/>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
       <c r="Q57" s="8"/>
       <c r="R57" s="8"/>
-      <c r="S57" s="8" t="str">
+      <c r="S57" s="8"/>
+      <c r="T57" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="T57" s="8"/>
       <c r="U57" s="8"/>
       <c r="V57" s="8"/>
       <c r="W57" s="8"/>
@@ -3477,910 +3717,910 @@
       <c r="AD57" s="8"/>
       <c r="AE57" s="8"/>
       <c r="AF57" s="8"/>
-    </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="S58" s="9" t="str">
+      <c r="AG57" s="8"/>
+    </row>
+    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="T58" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="S59" s="9" t="str">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="T59" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="S60" s="9" t="str">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="T60" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="S61" s="9" t="str">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="T61" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="S62" s="9" t="str">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="T62" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="S63" s="9" t="str">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="T63" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="S64" s="9" t="str">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="T64" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="65" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S65" s="9" t="str">
+    <row r="65" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T65" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="66" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S66" s="9" t="str">
+    <row r="66" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T66" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="67" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S67" s="9" t="str">
+    <row r="67" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T67" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="68" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S68" s="9" t="str">
+    <row r="68" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T68" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="69" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S69" s="9" t="str">
+    <row r="69" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T69" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="70" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S70" s="9" t="str">
+    <row r="70" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T70" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="71" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S71" s="9" t="str">
-        <f t="shared" ref="S71:S134" ca="1" si="1">IF(AND(P71&lt;TODAY(),S71&lt;&gt;"Cerrado"),"Vencido",S71)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S72" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S73" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S74" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S75" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S76" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S77" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S78" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S79" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S80" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S81" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S82" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S83" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S84" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S85" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S86" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S87" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S88" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S89" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="90" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S90" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S91" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S92" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="93" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S93" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="94" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S94" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="95" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S95" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="96" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S96" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="97" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S97" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="98" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S98" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="99" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S99" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="100" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S100" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="101" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S101" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S102" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="103" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S103" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S104" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="105" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S105" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="106" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S106" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S107" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="108" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S108" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="109" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S109" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="110" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S110" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="111" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S111" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S112" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S113" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="114" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S114" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="115" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S115" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S116" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="117" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S117" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="118" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S118" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="119" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S119" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="120" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S120" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="121" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S121" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S122" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="123" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S123" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="124" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S124" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S125" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="126" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S126" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="127" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S127" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="128" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S128" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="129" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S129" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="130" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S130" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S131" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="132" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S132" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S133" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S134" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="135" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S135" s="9" t="str">
-        <f t="shared" ref="S135:S198" ca="1" si="2">IF(AND(P135&lt;TODAY(),S135&lt;&gt;"Cerrado"),"Vencido",S135)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S136" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S137" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="138" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S138" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="139" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S139" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S140" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="141" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S141" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="142" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S142" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="143" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S143" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="144" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S144" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S145" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S146" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="147" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S147" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S148" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="149" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S149" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S150" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S151" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="152" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S152" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="153" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S153" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S154" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S155" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S156" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S157" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S158" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S159" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S160" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S161" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="162" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S162" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S163" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S164" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="165" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S165" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S166" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S167" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="168" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S168" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S169" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="170" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S170" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="171" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S171" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="172" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S172" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="173" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S173" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="174" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S174" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="175" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S175" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="176" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S176" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="177" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S177" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S178" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="179" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S179" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="180" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S180" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="181" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S181" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S182" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="183" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S183" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="184" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S184" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S185" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="186" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S186" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="187" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S187" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S188" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="189" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S189" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="190" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S190" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S191" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="192" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S192" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S193" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S194" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S195" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S196" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S197" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="198" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S198" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S199" s="9" t="str">
-        <f t="shared" ref="S199:S205" ca="1" si="3">IF(AND(P199&lt;TODAY(),S199&lt;&gt;"Cerrado"),"Vencido",S199)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S200" s="9" t="str">
+    <row r="71" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T71" s="9" t="str">
+        <f t="shared" ref="T71:T134" ca="1" si="1">IF(AND(Q71&lt;TODAY(),T71&lt;&gt;"Cerrado"),"Vencido",T71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T72" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T73" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T74" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T75" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T76" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T77" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T78" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T79" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T80" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T81" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T82" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T83" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T84" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T85" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T86" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T87" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T88" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T89" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T90" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T91" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T92" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T93" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T94" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T95" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T96" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T97" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T98" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T99" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T100" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T101" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T102" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T103" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T104" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T105" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T106" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T107" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T108" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T109" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T110" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T111" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T112" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T113" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T114" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T115" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T116" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T117" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T118" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T119" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T120" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T121" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T122" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T123" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T124" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T125" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T126" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="127" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T127" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T128" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T129" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T130" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T131" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="132" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T132" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="133" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T133" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T134" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T135" s="9" t="str">
+        <f t="shared" ref="T135:T198" ca="1" si="2">IF(AND(Q135&lt;TODAY(),T135&lt;&gt;"Cerrado"),"Vencido",T135)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T136" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T137" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="138" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T138" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T139" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T140" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T141" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T142" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="143" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T143" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="144" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T144" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T145" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T146" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="147" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T147" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T148" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T149" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T150" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T151" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T152" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T153" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="154" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T154" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="155" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T155" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T156" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T157" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T158" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T159" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="160" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T160" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T161" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="162" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T162" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="163" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T163" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T164" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T165" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T166" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T167" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="168" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T168" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T169" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="170" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T170" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="171" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T171" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="172" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T172" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="173" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T173" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T174" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T175" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="176" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T176" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="177" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T177" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="178" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T178" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="179" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T179" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="180" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T180" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="181" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T181" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="182" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T182" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="183" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T183" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="184" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T184" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="185" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T185" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="186" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T186" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="187" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T187" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="188" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T188" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="189" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T189" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="190" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T190" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="191" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T191" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="192" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T192" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="193" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T193" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="194" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T194" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="195" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T195" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="196" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T196" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="197" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T197" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="198" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T198" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="199" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T199" s="9" t="str">
+        <f t="shared" ref="T199:T205" ca="1" si="3">IF(AND(Q199&lt;TODAY(),T199&lt;&gt;"Cerrado"),"Vencido",T199)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T200" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="201" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S201" s="9" t="str">
+    <row r="201" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T201" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="202" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S202" s="9" t="str">
+    <row r="202" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T202" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="203" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S203" s="9" t="str">
+    <row r="203" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T203" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="204" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S204" s="9" t="str">
+    <row r="204" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T204" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="205" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S205" s="9" t="str">
+    <row r="205" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T205" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A11:A12"/>
-  </mergeCells>
+  <autoFilter ref="A1:AG13" xr:uid="{220792B3-42C8-4F5F-876D-A137B68C9789}"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="AA2:AA205" xr:uid="{274A9DB5-4743-4598-9019-2B28638E96CF}">
+    <dataValidation type="list" allowBlank="1" sqref="AB2:AB205" xr:uid="{274A9DB5-4743-4598-9019-2B28638E96CF}">
       <formula1>"Eficaz,Parcialmente eficaz,No eficaz"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="Z2:Z205" xr:uid="{16DC3DEB-B5C1-424F-80AB-A011FF6FFF69}">
+    <dataValidation type="list" allowBlank="1" sqref="AA2:AA205" xr:uid="{16DC3DEB-B5C1-424F-80AB-A011FF6FFF69}">
       <formula1>"Documental,Prueba de control,Reauditoría"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="AD2:AD205 W2:W205" xr:uid="{F29F231E-D84F-4213-8EDD-989663568A7C}">
+    <dataValidation type="list" allowBlank="1" sqref="AE2:AE205 X2:X205" xr:uid="{F29F231E-D84F-4213-8EDD-989663568A7C}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S2:S205" xr:uid="{58F37FD9-7546-4E93-BDBF-1230BE932915}">
+    <dataValidation type="list" allowBlank="1" sqref="T2:T205" xr:uid="{58F37FD9-7546-4E93-BDBF-1230BE932915}">
       <formula1>"Abierto,En proceso,Cerrado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4438,147 +4678,154 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD206"/>
+  <dimension ref="A1:AE206"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.88671875" style="9" customWidth="1"/>
     <col min="2" max="2" width="13.88671875" style="9" customWidth="1"/>
     <col min="3" max="3" width="16.88671875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" style="9" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="13" customWidth="1"/>
-    <col min="7" max="7" width="43.77734375" style="9" customWidth="1"/>
-    <col min="8" max="8" width="50.77734375" style="9" customWidth="1"/>
-    <col min="9" max="9" width="47.33203125" style="9" customWidth="1"/>
-    <col min="10" max="11" width="22" style="9" customWidth="1"/>
-    <col min="12" max="12" width="29.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="30" width="22" style="9" customWidth="1"/>
-    <col min="31" max="16384" width="8.77734375" style="9"/>
+    <col min="4" max="5" width="14.88671875" style="9" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="9" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" style="13" customWidth="1"/>
+    <col min="8" max="8" width="43.77734375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="50.77734375" style="9" customWidth="1"/>
+    <col min="10" max="10" width="47.33203125" style="9" customWidth="1"/>
+    <col min="11" max="12" width="22" style="9" customWidth="1"/>
+    <col min="13" max="13" width="29.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="31" width="22" style="9" customWidth="1"/>
+    <col min="32" max="16384" width="8.77734375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>46</v>
+        <v>162</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="G1" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>124</v>
-      </c>
       <c r="K1" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:30" s="22" customFormat="1" ht="66" x14ac:dyDescent="0.3">
-      <c r="A2" s="20"/>
+    <row r="2" spans="1:31" s="22" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+      <c r="A2" s="20" t="s">
+        <v>183</v>
+      </c>
       <c r="B2" s="21">
         <v>46143</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="20" t="s">
-        <v>160</v>
-      </c>
       <c r="H2" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="I2" s="20"/>
+        <v>156</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>155</v>
+      </c>
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
       <c r="N2" s="20"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="23"/>
       <c r="Q2" s="20"/>
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
@@ -4593,38 +4840,43 @@
       <c r="AB2" s="20"/>
       <c r="AC2" s="20"/>
       <c r="AD2" s="20"/>
-    </row>
-    <row r="3" spans="1:30" s="22" customFormat="1" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="20"/>
+      <c r="AE2" s="20"/>
+    </row>
+    <row r="3" spans="1:31" s="22" customFormat="1" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
+        <v>184</v>
+      </c>
       <c r="B3" s="21">
         <v>46143</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="20" t="s">
-        <v>162</v>
-      </c>
       <c r="H3" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="I3" s="20"/>
+        <v>158</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>157</v>
+      </c>
       <c r="J3" s="20"/>
       <c r="K3" s="20"/>
       <c r="L3" s="20"/>
       <c r="M3" s="20"/>
       <c r="N3" s="20"/>
-      <c r="O3" s="23"/>
-      <c r="P3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="23"/>
       <c r="Q3" s="20"/>
       <c r="R3" s="20"/>
       <c r="S3" s="20"/>
@@ -4639,38 +4891,43 @@
       <c r="AB3" s="20"/>
       <c r="AC3" s="20"/>
       <c r="AD3" s="20"/>
-    </row>
-    <row r="4" spans="1:30" s="22" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
+      <c r="AE3" s="20"/>
+    </row>
+    <row r="4" spans="1:31" s="22" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="20" t="s">
+        <v>185</v>
+      </c>
       <c r="B4" s="21">
         <v>46143</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G4" s="20" t="s">
-        <v>164</v>
-      </c>
       <c r="H4" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="I4" s="20"/>
+        <v>160</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>159</v>
+      </c>
       <c r="J4" s="20"/>
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
       <c r="M4" s="20"/>
       <c r="N4" s="20"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="23"/>
       <c r="Q4" s="20"/>
       <c r="R4" s="20"/>
       <c r="S4" s="20"/>
@@ -4685,38 +4942,43 @@
       <c r="AB4" s="20"/>
       <c r="AC4" s="20"/>
       <c r="AD4" s="20"/>
-    </row>
-    <row r="5" spans="1:30" s="22" customFormat="1" ht="66" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
+      <c r="AE4" s="20"/>
+    </row>
+    <row r="5" spans="1:31" s="22" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+      <c r="A5" s="20" t="s">
+        <v>186</v>
+      </c>
       <c r="B5" s="21">
         <v>46143</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>152</v>
+      <c r="G5" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="I5" s="20"/>
+        <v>148</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>149</v>
+      </c>
       <c r="J5" s="20"/>
       <c r="K5" s="20"/>
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
       <c r="N5" s="20"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="23"/>
       <c r="Q5" s="20"/>
       <c r="R5" s="20"/>
       <c r="S5" s="20"/>
@@ -4731,38 +4993,43 @@
       <c r="AB5" s="20"/>
       <c r="AC5" s="20"/>
       <c r="AD5" s="20"/>
-    </row>
-    <row r="6" spans="1:30" s="22" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="20"/>
+      <c r="AE5" s="20"/>
+    </row>
+    <row r="6" spans="1:31" s="22" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="20" t="s">
+        <v>187</v>
+      </c>
       <c r="B6" s="21">
         <v>46143</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="20" t="s">
-        <v>154</v>
-      </c>
       <c r="H6" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="I6" s="20"/>
+        <v>150</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>151</v>
+      </c>
       <c r="J6" s="20"/>
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="23"/>
       <c r="Q6" s="20"/>
       <c r="R6" s="20"/>
       <c r="S6" s="20"/>
@@ -4777,38 +5044,43 @@
       <c r="AB6" s="20"/>
       <c r="AC6" s="20"/>
       <c r="AD6" s="20"/>
-    </row>
-    <row r="7" spans="1:30" s="22" customFormat="1" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
+      <c r="AE6" s="20"/>
+    </row>
+    <row r="7" spans="1:31" s="22" customFormat="1" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
+        <v>188</v>
+      </c>
       <c r="B7" s="21">
         <v>46143</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>156</v>
+      <c r="G7" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="I7" s="20"/>
+        <v>152</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>153</v>
+      </c>
       <c r="J7" s="20"/>
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
       <c r="M7" s="20"/>
       <c r="N7" s="20"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="23"/>
       <c r="Q7" s="20"/>
       <c r="R7" s="20"/>
       <c r="S7" s="20"/>
@@ -4823,106 +5095,116 @@
       <c r="AB7" s="20"/>
       <c r="AC7" s="20"/>
       <c r="AD7" s="20"/>
-    </row>
-    <row r="8" spans="1:30" s="7" customFormat="1" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
+      <c r="AE7" s="20"/>
+    </row>
+    <row r="8" spans="1:31" s="7" customFormat="1" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
+        <v>189</v>
+      </c>
       <c r="B8" s="6">
         <v>45901</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="K8" s="5"/>
+      <c r="K8" s="5" t="s">
+        <v>122</v>
+      </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
-      <c r="O8" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5" t="str">
-        <f t="shared" ref="Q8:Q39" ca="1" si="0">IF(AND(N8&lt;TODAY(),Q8&lt;&gt;"Cerrado"),"Vencido",Q8)</f>
-        <v/>
-      </c>
-      <c r="R8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5" t="str">
+        <f t="shared" ref="R8:R39" ca="1" si="0">IF(AND(O8&lt;TODAY(),R8&lt;&gt;"Cerrado"),"Vencido",R8)</f>
+        <v/>
+      </c>
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
       <c r="W8" s="5"/>
-      <c r="X8" s="5" t="s">
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="Y8" s="5" t="s">
+      <c r="Z8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="Z8" s="5"/>
       <c r="AA8" s="5"/>
       <c r="AB8" s="5"/>
       <c r="AC8" s="5"/>
       <c r="AD8" s="5"/>
-    </row>
-    <row r="9" spans="1:30" s="11" customFormat="1" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
+      <c r="AE8" s="5"/>
+    </row>
+    <row r="9" spans="1:31" s="11" customFormat="1" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
+        <v>190</v>
+      </c>
       <c r="B9" s="6">
         <v>45901</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="K9" s="3"/>
+      <c r="K9" s="5" t="s">
+        <v>121</v>
+      </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3" t="str">
+      <c r="O9" s="3"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
@@ -4935,47 +5217,52 @@
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
-    </row>
-    <row r="10" spans="1:30" s="11" customFormat="1" ht="132" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
+      <c r="AE9" s="3"/>
+    </row>
+    <row r="10" spans="1:31" s="11" customFormat="1" ht="132" x14ac:dyDescent="0.3">
+      <c r="A10" s="20" t="s">
+        <v>191</v>
+      </c>
       <c r="B10" s="6">
         <v>45901</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="K10" s="3"/>
+      <c r="K10" s="7" t="s">
+        <v>123</v>
+      </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3" t="str">
+      <c r="O10" s="3"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -4988,47 +5275,52 @@
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
-    </row>
-    <row r="11" spans="1:30" s="11" customFormat="1" ht="250.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
+      <c r="AE10" s="3"/>
+    </row>
+    <row r="11" spans="1:31" s="11" customFormat="1" ht="250.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
+        <v>192</v>
+      </c>
       <c r="B11" s="6">
         <v>45901</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="I11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J11" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="K11" s="3"/>
+      <c r="K11" s="5" t="s">
+        <v>124</v>
+      </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3" t="str">
+      <c r="O11" s="3"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
@@ -5041,45 +5333,50 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" s="11" customFormat="1" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" s="11" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+      <c r="A12" s="20" t="s">
+        <v>193</v>
+      </c>
       <c r="B12" s="6">
         <v>45778</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="J12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-      <c r="Q12" s="3" t="str">
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
@@ -5092,45 +5389,50 @@
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
-    </row>
-    <row r="13" spans="1:30" s="11" customFormat="1" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
+      <c r="AE12" s="3"/>
+    </row>
+    <row r="13" spans="1:31" s="11" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+      <c r="A13" s="20" t="s">
+        <v>194</v>
+      </c>
       <c r="B13" s="6">
         <v>45778</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J13" s="3"/>
+      <c r="J13" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
-      <c r="Q13" s="3" t="str">
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
@@ -5143,45 +5445,50 @@
       <c r="AB13" s="3"/>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
-    </row>
-    <row r="14" spans="1:30" s="11" customFormat="1" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
+      <c r="AE13" s="3"/>
+    </row>
+    <row r="14" spans="1:31" s="11" customFormat="1" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>195</v>
+      </c>
       <c r="B14" s="6">
         <v>45778</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="H14" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J14" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
-      <c r="Q14" s="3" t="str">
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
@@ -5194,45 +5501,50 @@
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
-    </row>
-    <row r="15" spans="1:30" s="11" customFormat="1" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
+      <c r="AE14" s="3"/>
+    </row>
+    <row r="15" spans="1:31" s="11" customFormat="1" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="20" t="s">
+        <v>196</v>
+      </c>
       <c r="B15" s="6">
         <v>45778</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
-      <c r="Q15" s="3" t="str">
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R15" s="3"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
@@ -5245,45 +5557,50 @@
       <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
-    </row>
-    <row r="16" spans="1:30" s="11" customFormat="1" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
+      <c r="AE15" s="3"/>
+    </row>
+    <row r="16" spans="1:31" s="11" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+      <c r="A16" s="20" t="s">
+        <v>197</v>
+      </c>
       <c r="B16" s="6">
         <v>45778</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="H16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J16" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-      <c r="Q16" s="3" t="str">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -5296,45 +5613,50 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="1:30" s="11" customFormat="1" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="1:31" s="11" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+      <c r="A17" s="20" t="s">
+        <v>198</v>
+      </c>
       <c r="B17" s="6">
         <v>45778</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>55</v>
+        <v>165</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J17" s="3"/>
+        <v>52</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
-      <c r="Q17" s="3" t="str">
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R17" s="3"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
@@ -5347,45 +5669,50 @@
       <c r="AB17" s="3"/>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
-    </row>
-    <row r="18" spans="1:30" s="11" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
+      <c r="AE17" s="3"/>
+    </row>
+    <row r="18" spans="1:31" s="11" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="20" t="s">
+        <v>199</v>
+      </c>
       <c r="B18" s="6">
         <v>45505</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>61</v>
+        <v>164</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F18" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
-      <c r="Q18" s="3" t="str">
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R18" s="3"/>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
@@ -5398,45 +5725,50 @@
       <c r="AB18" s="3"/>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
-    </row>
-    <row r="19" spans="1:30" s="11" customFormat="1" ht="66" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
+      <c r="AE18" s="3"/>
+    </row>
+    <row r="19" spans="1:31" s="11" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+      <c r="A19" s="20" t="s">
+        <v>200</v>
+      </c>
       <c r="B19" s="6">
         <v>45505</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J19" s="3"/>
+      <c r="J19" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-      <c r="Q19" s="3" t="str">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
@@ -5449,45 +5781,50 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="1:30" s="11" customFormat="1" ht="66" x14ac:dyDescent="0.3">
-      <c r="A20" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="1:31" s="11" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+      <c r="A20" s="20" t="s">
+        <v>201</v>
+      </c>
       <c r="B20" s="6">
         <v>45505</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>61</v>
+        <v>164</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F20" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="H20" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="J20" s="3"/>
+        <v>69</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
-      <c r="Q20" s="3" t="str">
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R20" s="3"/>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
@@ -5500,45 +5837,50 @@
       <c r="AB20" s="3"/>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
-    </row>
-    <row r="21" spans="1:30" s="11" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
+      <c r="AE20" s="3"/>
+    </row>
+    <row r="21" spans="1:31" s="11" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="20" t="s">
+        <v>202</v>
+      </c>
       <c r="B21" s="6">
         <v>45505</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>61</v>
+        <v>164</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>74</v>
+        <v>166</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
-      <c r="Q21" s="3" t="str">
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R21" s="3"/>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
@@ -5551,45 +5893,50 @@
       <c r="AB21" s="3"/>
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
-    </row>
-    <row r="22" spans="1:30" s="11" customFormat="1" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
+      <c r="AE21" s="3"/>
+    </row>
+    <row r="22" spans="1:31" s="11" customFormat="1" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>203</v>
+      </c>
       <c r="B22" s="6">
         <v>45505</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>61</v>
+        <v>164</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F22" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
-      <c r="Q22" s="3" t="str">
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R22" s="3"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
@@ -5602,31 +5949,36 @@
       <c r="AB22" s="3"/>
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
-    </row>
-    <row r="23" spans="1:30" s="11" customFormat="1" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
+      <c r="AE22" s="3"/>
+    </row>
+    <row r="23" spans="1:31" s="11" customFormat="1" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="20" t="s">
+        <v>204</v>
+      </c>
       <c r="B23" s="6">
         <v>45505</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>61</v>
+        <v>164</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>80</v>
+        <v>166</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="I23" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
@@ -5634,11 +5986,11 @@
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
-      <c r="Q23" s="3" t="str">
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
@@ -5651,45 +6003,50 @@
       <c r="AB23" s="3"/>
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
-    </row>
-    <row r="24" spans="1:30" s="11" customFormat="1" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3"/>
+      <c r="AE23" s="3"/>
+    </row>
+    <row r="24" spans="1:31" s="11" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="20" t="s">
+        <v>205</v>
+      </c>
       <c r="B24" s="6">
         <v>45413</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
-      <c r="Q24" s="3" t="str">
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R24" s="3"/>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
@@ -5702,45 +6059,50 @@
       <c r="AB24" s="3"/>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
-    </row>
-    <row r="25" spans="1:30" s="11" customFormat="1" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="3"/>
+      <c r="AE24" s="3"/>
+    </row>
+    <row r="25" spans="1:31" s="11" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="20" t="s">
+        <v>206</v>
+      </c>
       <c r="B25" s="6">
         <v>45413</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>84</v>
+        <v>163</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F25" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="I25" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="J25" s="3"/>
+        <v>86</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
-      <c r="Q25" s="3" t="str">
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R25" s="3"/>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
@@ -5753,15 +6115,16 @@
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
-    </row>
-    <row r="26" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE25" s="3"/>
+    </row>
+    <row r="26" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="5"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
@@ -5771,11 +6134,11 @@
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
-      <c r="Q26" s="3" t="str">
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R26" s="3"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
@@ -5788,15 +6151,16 @@
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
-    </row>
-    <row r="27" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE26" s="3"/>
+    </row>
+    <row r="27" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="5"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
@@ -5806,11 +6170,11 @@
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
-      <c r="Q27" s="3" t="str">
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R27" s="3"/>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
@@ -5823,15 +6187,16 @@
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
-    </row>
-    <row r="28" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE27" s="3"/>
+    </row>
+    <row r="28" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="5"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
@@ -5841,11 +6206,11 @@
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
-      <c r="Q28" s="3" t="str">
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R28" s="3"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
@@ -5858,15 +6223,16 @@
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
       <c r="AD28" s="3"/>
-    </row>
-    <row r="29" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE28" s="3"/>
+    </row>
+    <row r="29" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="5"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -5876,11 +6242,11 @@
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
-      <c r="Q29" s="3" t="str">
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R29" s="3"/>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
@@ -5893,15 +6259,16 @@
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
-    </row>
-    <row r="30" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE29" s="3"/>
+    </row>
+    <row r="30" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="5"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -5911,11 +6278,11 @@
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
-      <c r="Q30" s="3" t="str">
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
@@ -5928,15 +6295,16 @@
       <c r="AB30" s="3"/>
       <c r="AC30" s="3"/>
       <c r="AD30" s="3"/>
-    </row>
-    <row r="31" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE30" s="3"/>
+    </row>
+    <row r="31" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="5"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -5946,11 +6314,11 @@
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
-      <c r="Q31" s="3" t="str">
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R31" s="3"/>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
@@ -5963,15 +6331,16 @@
       <c r="AB31" s="3"/>
       <c r="AC31" s="3"/>
       <c r="AD31" s="3"/>
-    </row>
-    <row r="32" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE31" s="3"/>
+    </row>
+    <row r="32" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="5"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -5981,11 +6350,11 @@
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
-      <c r="Q32" s="3" t="str">
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R32" s="3"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
@@ -5998,15 +6367,16 @@
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
       <c r="AD32" s="3"/>
-    </row>
-    <row r="33" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE32" s="3"/>
+    </row>
+    <row r="33" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="5"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
@@ -6016,11 +6386,11 @@
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
-      <c r="Q33" s="3" t="str">
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R33" s="3"/>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
@@ -6033,15 +6403,16 @@
       <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
-    </row>
-    <row r="34" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE33" s="3"/>
+    </row>
+    <row r="34" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="5"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
@@ -6051,11 +6422,11 @@
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
-      <c r="Q34" s="3" t="str">
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R34" s="3"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
@@ -6068,15 +6439,16 @@
       <c r="AB34" s="3"/>
       <c r="AC34" s="3"/>
       <c r="AD34" s="3"/>
-    </row>
-    <row r="35" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE34" s="3"/>
+    </row>
+    <row r="35" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="5"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
@@ -6086,11 +6458,11 @@
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
-      <c r="Q35" s="3" t="str">
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R35" s="3"/>
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
@@ -6103,15 +6475,16 @@
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
-    </row>
-    <row r="36" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE35" s="3"/>
+    </row>
+    <row r="36" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="5"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
@@ -6121,11 +6494,11 @@
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
-      <c r="Q36" s="3" t="str">
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R36" s="3"/>
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
@@ -6138,15 +6511,16 @@
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
-    </row>
-    <row r="37" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE36" s="3"/>
+    </row>
+    <row r="37" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="5"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
@@ -6156,11 +6530,11 @@
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
-      <c r="Q37" s="3" t="str">
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R37" s="3"/>
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
@@ -6173,15 +6547,16 @@
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
       <c r="AD37" s="3"/>
-    </row>
-    <row r="38" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE37" s="3"/>
+    </row>
+    <row r="38" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="5"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
@@ -6191,11 +6566,11 @@
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
-      <c r="Q38" s="3" t="str">
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R38" s="3"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
@@ -6208,15 +6583,16 @@
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
       <c r="AD38" s="3"/>
-    </row>
-    <row r="39" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE38" s="3"/>
+    </row>
+    <row r="39" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="5"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
@@ -6226,11 +6602,11 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-      <c r="Q39" s="3" t="str">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
@@ -6243,15 +6619,16 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="5"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
@@ -6261,11 +6638,11 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-      <c r="Q40" s="3" t="str">
-        <f t="shared" ref="Q40:Q71" ca="1" si="1">IF(AND(N40&lt;TODAY(),Q40&lt;&gt;"Cerrado"),"Vencido",Q40)</f>
-        <v/>
-      </c>
-      <c r="R40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3" t="str">
+        <f t="shared" ref="R40:R71" ca="1" si="1">IF(AND(O40&lt;TODAY(),R40&lt;&gt;"Cerrado"),"Vencido",R40)</f>
+        <v/>
+      </c>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
@@ -6278,15 +6655,16 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="5"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
@@ -6296,11 +6674,11 @@
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
-      <c r="Q41" s="3" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -6313,15 +6691,16 @@
       <c r="AB41" s="3"/>
       <c r="AC41" s="3"/>
       <c r="AD41" s="3"/>
-    </row>
-    <row r="42" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE41" s="3"/>
+    </row>
+    <row r="42" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="5"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
@@ -6331,11 +6710,11 @@
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
-      <c r="Q42" s="3" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
@@ -6348,15 +6727,16 @@
       <c r="AB42" s="3"/>
       <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
-    </row>
-    <row r="43" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE42" s="3"/>
+    </row>
+    <row r="43" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="5"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
@@ -6366,11 +6746,11 @@
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
-      <c r="Q43" s="3" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R43" s="3"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
@@ -6383,15 +6763,16 @@
       <c r="AB43" s="3"/>
       <c r="AC43" s="3"/>
       <c r="AD43" s="3"/>
-    </row>
-    <row r="44" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE43" s="3"/>
+    </row>
+    <row r="44" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="5"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
@@ -6401,11 +6782,11 @@
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
-      <c r="Q44" s="3" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
@@ -6418,15 +6799,16 @@
       <c r="AB44" s="3"/>
       <c r="AC44" s="3"/>
       <c r="AD44" s="3"/>
-    </row>
-    <row r="45" spans="1:30" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="AE44" s="3"/>
+    </row>
+    <row r="45" spans="1:31" s="11" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="5"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -6436,11 +6818,11 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3"/>
-      <c r="Q45" s="3" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S45" s="3"/>
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
@@ -6453,15 +6835,16 @@
       <c r="AB45" s="3"/>
       <c r="AC45" s="3"/>
       <c r="AD45" s="3"/>
-    </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE45" s="3"/>
+    </row>
+    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="12"/>
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
       <c r="J46" s="8"/>
@@ -6471,11 +6854,11 @@
       <c r="N46" s="8"/>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
-      <c r="Q46" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R46" s="8"/>
+      <c r="Q46" s="8"/>
+      <c r="R46" s="8" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S46" s="8"/>
       <c r="T46" s="8"/>
       <c r="U46" s="8"/>
@@ -6488,15 +6871,16 @@
       <c r="AB46" s="8"/>
       <c r="AC46" s="8"/>
       <c r="AD46" s="8"/>
-    </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE46" s="8"/>
+    </row>
+    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="12"/>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
@@ -6506,11 +6890,11 @@
       <c r="N47" s="8"/>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
-      <c r="Q47" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R47" s="8"/>
+      <c r="Q47" s="8"/>
+      <c r="R47" s="8" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S47" s="8"/>
       <c r="T47" s="8"/>
       <c r="U47" s="8"/>
@@ -6523,15 +6907,16 @@
       <c r="AB47" s="8"/>
       <c r="AC47" s="8"/>
       <c r="AD47" s="8"/>
-    </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE47" s="8"/>
+    </row>
+    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="12"/>
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
@@ -6541,11 +6926,11 @@
       <c r="N48" s="8"/>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
-      <c r="Q48" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R48" s="8"/>
+      <c r="Q48" s="8"/>
+      <c r="R48" s="8" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S48" s="8"/>
       <c r="T48" s="8"/>
       <c r="U48" s="8"/>
@@ -6558,15 +6943,16 @@
       <c r="AB48" s="8"/>
       <c r="AC48" s="8"/>
       <c r="AD48" s="8"/>
-    </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE48" s="8"/>
+    </row>
+    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="12"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
@@ -6576,11 +6962,11 @@
       <c r="N49" s="8"/>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
-      <c r="Q49" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R49" s="8"/>
+      <c r="Q49" s="8"/>
+      <c r="R49" s="8" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S49" s="8"/>
       <c r="T49" s="8"/>
       <c r="U49" s="8"/>
@@ -6593,15 +6979,16 @@
       <c r="AB49" s="8"/>
       <c r="AC49" s="8"/>
       <c r="AD49" s="8"/>
-    </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE49" s="8"/>
+    </row>
+    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="12"/>
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
@@ -6611,11 +6998,11 @@
       <c r="N50" s="8"/>
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
-      <c r="Q50" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R50" s="8"/>
+      <c r="Q50" s="8"/>
+      <c r="R50" s="8" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S50" s="8"/>
       <c r="T50" s="8"/>
       <c r="U50" s="8"/>
@@ -6628,15 +7015,16 @@
       <c r="AB50" s="8"/>
       <c r="AC50" s="8"/>
       <c r="AD50" s="8"/>
-    </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE50" s="8"/>
+    </row>
+    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="12"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
@@ -6646,11 +7034,11 @@
       <c r="N51" s="8"/>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
-      <c r="Q51" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R51" s="8"/>
+      <c r="Q51" s="8"/>
+      <c r="R51" s="8" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S51" s="8"/>
       <c r="T51" s="8"/>
       <c r="U51" s="8"/>
@@ -6663,15 +7051,16 @@
       <c r="AB51" s="8"/>
       <c r="AC51" s="8"/>
       <c r="AD51" s="8"/>
-    </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE51" s="8"/>
+    </row>
+    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="12"/>
       <c r="H52" s="8"/>
       <c r="I52" s="8"/>
       <c r="J52" s="8"/>
@@ -6681,11 +7070,11 @@
       <c r="N52" s="8"/>
       <c r="O52" s="8"/>
       <c r="P52" s="8"/>
-      <c r="Q52" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R52" s="8"/>
+      <c r="Q52" s="8"/>
+      <c r="R52" s="8" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S52" s="8"/>
       <c r="T52" s="8"/>
       <c r="U52" s="8"/>
@@ -6698,15 +7087,16 @@
       <c r="AB52" s="8"/>
       <c r="AC52" s="8"/>
       <c r="AD52" s="8"/>
-    </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE52" s="8"/>
+    </row>
+    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="12"/>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
@@ -6716,11 +7106,11 @@
       <c r="N53" s="8"/>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
-      <c r="Q53" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R53" s="8"/>
+      <c r="Q53" s="8"/>
+      <c r="R53" s="8" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S53" s="8"/>
       <c r="T53" s="8"/>
       <c r="U53" s="8"/>
@@ -6733,15 +7123,16 @@
       <c r="AB53" s="8"/>
       <c r="AC53" s="8"/>
       <c r="AD53" s="8"/>
-    </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE53" s="8"/>
+    </row>
+    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="12"/>
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
       <c r="J54" s="8"/>
@@ -6751,11 +7142,11 @@
       <c r="N54" s="8"/>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
-      <c r="Q54" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R54" s="8"/>
+      <c r="Q54" s="8"/>
+      <c r="R54" s="8" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S54" s="8"/>
       <c r="T54" s="8"/>
       <c r="U54" s="8"/>
@@ -6768,15 +7159,16 @@
       <c r="AB54" s="8"/>
       <c r="AC54" s="8"/>
       <c r="AD54" s="8"/>
-    </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE54" s="8"/>
+    </row>
+    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="12"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
@@ -6786,11 +7178,11 @@
       <c r="N55" s="8"/>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
-      <c r="Q55" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R55" s="8"/>
+      <c r="Q55" s="8"/>
+      <c r="R55" s="8" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S55" s="8"/>
       <c r="T55" s="8"/>
       <c r="U55" s="8"/>
@@ -6803,15 +7195,16 @@
       <c r="AB55" s="8"/>
       <c r="AC55" s="8"/>
       <c r="AD55" s="8"/>
-    </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE55" s="8"/>
+    </row>
+    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="12"/>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
       <c r="J56" s="8"/>
@@ -6821,11 +7214,11 @@
       <c r="N56" s="8"/>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
-      <c r="Q56" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R56" s="8"/>
+      <c r="Q56" s="8"/>
+      <c r="R56" s="8" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S56" s="8"/>
       <c r="T56" s="8"/>
       <c r="U56" s="8"/>
@@ -6838,15 +7231,16 @@
       <c r="AB56" s="8"/>
       <c r="AC56" s="8"/>
       <c r="AD56" s="8"/>
-    </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE56" s="8"/>
+    </row>
+    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="8"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="12"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
@@ -6856,11 +7250,11 @@
       <c r="N57" s="8"/>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
-      <c r="Q57" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R57" s="8"/>
+      <c r="Q57" s="8"/>
+      <c r="R57" s="8" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S57" s="8"/>
       <c r="T57" s="8"/>
       <c r="U57" s="8"/>
@@ -6873,15 +7267,16 @@
       <c r="AB57" s="8"/>
       <c r="AC57" s="8"/>
       <c r="AD57" s="8"/>
-    </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE57" s="8"/>
+    </row>
+    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="12"/>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
@@ -6891,11 +7286,11 @@
       <c r="N58" s="8"/>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
-      <c r="Q58" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R58" s="8"/>
+      <c r="Q58" s="8"/>
+      <c r="R58" s="8" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="S58" s="8"/>
       <c r="T58" s="8"/>
       <c r="U58" s="8"/>
@@ -6908,925 +7303,926 @@
       <c r="AB58" s="8"/>
       <c r="AC58" s="8"/>
       <c r="AD58" s="8"/>
-    </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="Q59" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="Q60" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="Q61" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="Q62" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="Q63" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="Q64" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q65" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q66" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q67" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q68" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q69" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q70" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q71" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q72" s="9" t="str">
-        <f t="shared" ref="Q72:Q103" ca="1" si="2">IF(AND(N72&lt;TODAY(),Q72&lt;&gt;"Cerrado"),"Vencido",Q72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q73" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q74" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q75" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q76" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q77" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q78" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q79" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q80" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q81" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q82" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q83" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q84" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q85" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q86" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q87" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q88" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q89" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="90" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q90" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q91" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q92" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="93" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q93" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="94" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q94" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="95" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q95" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="96" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q96" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="97" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q97" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="98" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q98" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="99" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q99" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="100" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q100" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="101" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q101" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q102" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="103" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q103" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q104" s="9" t="str">
-        <f t="shared" ref="Q104:Q135" ca="1" si="3">IF(AND(N104&lt;TODAY(),Q104&lt;&gt;"Cerrado"),"Vencido",Q104)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q105" s="9" t="str">
+      <c r="AE58" s="8"/>
+    </row>
+    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="R59" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="R60" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="R61" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="R62" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="R63" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="R64" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R65" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R66" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R67" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R68" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R69" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R70" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R71" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R72" s="9" t="str">
+        <f t="shared" ref="R72:R103" ca="1" si="2">IF(AND(O72&lt;TODAY(),R72&lt;&gt;"Cerrado"),"Vencido",R72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R73" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R74" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R75" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R76" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R77" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R78" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R79" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R80" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R81" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R82" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R83" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R84" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R85" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R86" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R87" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R88" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R89" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R90" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R91" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R92" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R93" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R94" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R95" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R96" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R97" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R98" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R99" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R100" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R101" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R102" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R103" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R104" s="9" t="str">
+        <f t="shared" ref="R104:R135" ca="1" si="3">IF(AND(O104&lt;TODAY(),R104&lt;&gt;"Cerrado"),"Vencido",R104)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R105" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="106" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q106" s="9" t="str">
+    <row r="106" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R106" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="107" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q107" s="9" t="str">
+    <row r="107" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R107" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="108" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q108" s="9" t="str">
+    <row r="108" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R108" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="109" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q109" s="9" t="str">
+    <row r="109" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R109" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="110" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q110" s="9" t="str">
+    <row r="110" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R110" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="111" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q111" s="9" t="str">
+    <row r="111" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R111" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="112" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q112" s="9" t="str">
+    <row r="112" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R112" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="113" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q113" s="9" t="str">
+    <row r="113" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R113" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="114" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q114" s="9" t="str">
+    <row r="114" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R114" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="115" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q115" s="9" t="str">
+    <row r="115" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R115" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="116" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q116" s="9" t="str">
+    <row r="116" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R116" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="117" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q117" s="9" t="str">
+    <row r="117" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R117" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q118" s="9" t="str">
+    <row r="118" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R118" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q119" s="9" t="str">
+    <row r="119" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R119" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q120" s="9" t="str">
+    <row r="120" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R120" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q121" s="9" t="str">
+    <row r="121" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R121" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="122" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q122" s="9" t="str">
+    <row r="122" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R122" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="123" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q123" s="9" t="str">
+    <row r="123" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R123" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="124" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q124" s="9" t="str">
+    <row r="124" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R124" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="125" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q125" s="9" t="str">
+    <row r="125" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R125" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="126" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q126" s="9" t="str">
+    <row r="126" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R126" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="127" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q127" s="9" t="str">
+    <row r="127" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R127" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="128" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q128" s="9" t="str">
+    <row r="128" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R128" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="129" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q129" s="9" t="str">
+    <row r="129" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R129" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="130" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q130" s="9" t="str">
+    <row r="130" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R130" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="131" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q131" s="9" t="str">
+    <row r="131" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R131" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="132" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q132" s="9" t="str">
+    <row r="132" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R132" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="133" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q133" s="9" t="str">
+    <row r="133" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R133" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="134" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q134" s="9" t="str">
+    <row r="134" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R134" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="135" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q135" s="9" t="str">
+    <row r="135" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R135" s="9" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="136" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q136" s="9" t="str">
-        <f t="shared" ref="Q136:Q167" ca="1" si="4">IF(AND(N136&lt;TODAY(),Q136&lt;&gt;"Cerrado"),"Vencido",Q136)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q137" s="9" t="str">
+    <row r="136" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R136" s="9" t="str">
+        <f t="shared" ref="R136:R167" ca="1" si="4">IF(AND(O136&lt;TODAY(),R136&lt;&gt;"Cerrado"),"Vencido",R136)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R137" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="138" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q138" s="9" t="str">
+    <row r="138" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R138" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="139" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q139" s="9" t="str">
+    <row r="139" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R139" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="140" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q140" s="9" t="str">
+    <row r="140" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R140" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="141" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q141" s="9" t="str">
+    <row r="141" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R141" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="142" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q142" s="9" t="str">
+    <row r="142" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R142" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="143" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q143" s="9" t="str">
+    <row r="143" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R143" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="144" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q144" s="9" t="str">
+    <row r="144" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R144" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="145" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q145" s="9" t="str">
+    <row r="145" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R145" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="146" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q146" s="9" t="str">
+    <row r="146" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R146" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="147" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q147" s="9" t="str">
+    <row r="147" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R147" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="148" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q148" s="9" t="str">
+    <row r="148" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R148" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="149" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q149" s="9" t="str">
+    <row r="149" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R149" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="150" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q150" s="9" t="str">
+    <row r="150" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R150" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="151" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q151" s="9" t="str">
+    <row r="151" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R151" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="152" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q152" s="9" t="str">
+    <row r="152" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R152" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="153" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q153" s="9" t="str">
+    <row r="153" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R153" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="154" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q154" s="9" t="str">
+    <row r="154" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R154" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="155" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q155" s="9" t="str">
+    <row r="155" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R155" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="156" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q156" s="9" t="str">
+    <row r="156" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R156" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="157" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q157" s="9" t="str">
+    <row r="157" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R157" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="158" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q158" s="9" t="str">
+    <row r="158" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R158" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="159" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q159" s="9" t="str">
+    <row r="159" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R159" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="160" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q160" s="9" t="str">
+    <row r="160" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R160" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="161" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q161" s="9" t="str">
+    <row r="161" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R161" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="162" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q162" s="9" t="str">
+    <row r="162" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R162" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="163" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q163" s="9" t="str">
+    <row r="163" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R163" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="164" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q164" s="9" t="str">
+    <row r="164" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R164" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="165" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q165" s="9" t="str">
+    <row r="165" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R165" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="166" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q166" s="9" t="str">
+    <row r="166" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R166" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="167" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q167" s="9" t="str">
+    <row r="167" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R167" s="9" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="168" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q168" s="9" t="str">
-        <f t="shared" ref="Q168:Q199" ca="1" si="5">IF(AND(N168&lt;TODAY(),Q168&lt;&gt;"Cerrado"),"Vencido",Q168)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q169" s="9" t="str">
+    <row r="168" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R168" s="9" t="str">
+        <f t="shared" ref="R168:R199" ca="1" si="5">IF(AND(O168&lt;TODAY(),R168&lt;&gt;"Cerrado"),"Vencido",R168)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R169" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="170" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q170" s="9" t="str">
+    <row r="170" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R170" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="171" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q171" s="9" t="str">
+    <row r="171" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R171" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="172" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q172" s="9" t="str">
+    <row r="172" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R172" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="173" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q173" s="9" t="str">
+    <row r="173" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R173" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="174" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q174" s="9" t="str">
+    <row r="174" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R174" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="175" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q175" s="9" t="str">
+    <row r="175" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R175" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="176" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q176" s="9" t="str">
+    <row r="176" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R176" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="177" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q177" s="9" t="str">
+    <row r="177" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R177" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="178" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q178" s="9" t="str">
+    <row r="178" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R178" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="179" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q179" s="9" t="str">
+    <row r="179" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R179" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="180" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q180" s="9" t="str">
+    <row r="180" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R180" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="181" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q181" s="9" t="str">
+    <row r="181" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R181" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="182" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q182" s="9" t="str">
+    <row r="182" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R182" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="183" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q183" s="9" t="str">
+    <row r="183" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R183" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="184" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q184" s="9" t="str">
+    <row r="184" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R184" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="185" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q185" s="9" t="str">
+    <row r="185" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R185" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="186" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q186" s="9" t="str">
+    <row r="186" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R186" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="187" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q187" s="9" t="str">
+    <row r="187" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R187" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="188" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q188" s="9" t="str">
+    <row r="188" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R188" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="189" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q189" s="9" t="str">
+    <row r="189" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R189" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="190" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q190" s="9" t="str">
+    <row r="190" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R190" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="191" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q191" s="9" t="str">
+    <row r="191" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R191" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="192" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q192" s="9" t="str">
+    <row r="192" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R192" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="193" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q193" s="9" t="str">
+    <row r="193" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R193" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="194" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q194" s="9" t="str">
+    <row r="194" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R194" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="195" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q195" s="9" t="str">
+    <row r="195" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R195" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="196" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q196" s="9" t="str">
+    <row r="196" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R196" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="197" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q197" s="9" t="str">
+    <row r="197" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R197" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="198" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q198" s="9" t="str">
+    <row r="198" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R198" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="199" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q199" s="9" t="str">
+    <row r="199" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R199" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="200" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q200" s="9" t="str">
-        <f t="shared" ref="Q200:Q206" ca="1" si="6">IF(AND(N200&lt;TODAY(),Q200&lt;&gt;"Cerrado"),"Vencido",Q200)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q201" s="9" t="str">
+    <row r="200" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R200" s="9" t="str">
+        <f t="shared" ref="R200:R206" ca="1" si="6">IF(AND(O200&lt;TODAY(),R200&lt;&gt;"Cerrado"),"Vencido",R200)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R201" s="9" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="202" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q202" s="9" t="str">
+    <row r="202" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R202" s="9" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="203" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q203" s="9" t="str">
+    <row r="203" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R203" s="9" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="204" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q204" s="9" t="str">
+    <row r="204" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R204" s="9" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="205" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q205" s="9" t="str">
+    <row r="205" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R205" s="9" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="206" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q206" s="9" t="str">
+    <row r="206" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R206" s="9" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD206" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
-    <mergeCell ref="O8:O11"/>
+    <mergeCell ref="P8:P11"/>
   </mergeCells>
-  <conditionalFormatting sqref="F1:F1048576">
+  <phoneticPr fontId="6" type="noConversion"/>
+  <conditionalFormatting sqref="G1:G1048576">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Bajo">
-      <formula>NOT(ISERROR(SEARCH("Bajo",F1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Bajo",G1)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Medio">
-      <formula>NOT(ISERROR(SEARCH("Medio",F1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Medio",G1)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Alto">
-      <formula>NOT(ISERROR(SEARCH("Alto",F1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Alto",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="Q8:Q206" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="R8:R206" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Abierto,En proceso,Cerrado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="U8:U206 AB8:AB206" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="V8:V206 AC8:AC206" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="X8:X206" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="Y8:Y206" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Documental,Prueba de control,Reauditoría"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="Y8:Y206" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="Z8:Z206" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Eficaz,Parcialmente eficaz,No eficaz"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F206" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G206" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Alto,Medio,Bajo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7853,7 +8249,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="str">
-        <f ca="1">COUNTIF('Base Hallazgos Aseguramiento'!Q:Q,"Cerrado")/COUNTA('Base Hallazgos Aseguramiento'!C:C)</f>
+        <f ca="1">COUNTIF('Base Hallazgos Aseguramiento'!R:R,"Cerrado")/COUNTA('Base Hallazgos Aseguramiento'!C:C)</f>
         <v/>
       </c>
     </row>
@@ -7862,7 +8258,7 @@
         <v>29</v>
       </c>
       <c r="B4" t="str">
-        <f ca="1">COUNTIF('Base Hallazgos Aseguramiento'!Q:Q,"Vencido")/COUNTA('Base Hallazgos Aseguramiento'!C:C)</f>
+        <f ca="1">COUNTIF('Base Hallazgos Aseguramiento'!R:R,"Vencido")/COUNTA('Base Hallazgos Aseguramiento'!C:C)</f>
         <v/>
       </c>
     </row>
@@ -7880,7 +8276,7 @@
         <v>31</v>
       </c>
       <c r="B6">
-        <f>COUNTIF('Base Hallazgos Aseguramiento'!F:F,"Alto")</f>
+        <f>COUNTIF('Base Hallazgos Aseguramiento'!G:G,"Alto")</f>
         <v>16</v>
       </c>
     </row>

--- a/data/Matriz_Seguimiento_Hallazgos.xlsx
+++ b/data/Matriz_Seguimiento_Hallazgos.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="603" documentId="8_{B9D78422-FDFF-47F2-8818-479A70B2C122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{382B4E11-A690-47A1-9445-EA0F808FD212}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base Hallazgos SIG" sheetId="4" r:id="rId1"/>
@@ -942,10 +942,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5199,7 +5199,7 @@
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
-      <c r="P9" s="28"/>
+      <c r="P9" s="27"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5257,7 +5257,7 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
-      <c r="P10" s="28"/>
+      <c r="P10" s="27"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5315,7 +5315,7 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-      <c r="P11" s="27"/>
+      <c r="P11" s="28"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3" t="str">
         <f t="shared" ca="1" si="0"/>

--- a/data/Matriz_Seguimiento_Hallazgos.xlsx
+++ b/data/Matriz_Seguimiento_Hallazgos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Dashboard-Auditoria/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="603" documentId="8_{B9D78422-FDFF-47F2-8818-479A70B2C122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{382B4E11-A690-47A1-9445-EA0F808FD212}"/>
+  <xr:revisionPtr revIDLastSave="610" documentId="8_{B9D78422-FDFF-47F2-8818-479A70B2C122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B125148E-1686-49F3-9828-28C0A12EF2C9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,13 +16,14 @@
     <sheet name="Base Hallazgos SIG" sheetId="4" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="5" state="hidden" r:id="rId2"/>
     <sheet name="Base Hallazgos Aseguramiento" sheetId="1" r:id="rId3"/>
-    <sheet name="Dashboard_Comité" sheetId="2" state="hidden" r:id="rId4"/>
+    <sheet name="Hoja1" sheetId="6" r:id="rId4"/>
+    <sheet name="Dashboard_Comité" sheetId="2" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Base Hallazgos Aseguramiento'!$A$1:$AE$206</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base Hallazgos SIG'!$A$1:$AG$13</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="210">
   <si>
     <t>Código Hallazgo</t>
   </si>
@@ -734,12 +735,21 @@
   <si>
     <t>HASEG-24</t>
   </si>
+  <si>
+    <t>proceso</t>
+  </si>
+  <si>
+    <t>fuente</t>
+  </si>
+  <si>
+    <t>observaciones o oportunidades</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -785,8 +795,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -802,6 +820,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -870,7 +894,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -948,6 +972,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4608,7 +4633,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG13" xr:uid="{220792B3-42C8-4F5F-876D-A137B68C9789}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="AB2:AB205" xr:uid="{274A9DB5-4743-4598-9019-2B28638E96CF}">
@@ -8232,6 +8256,27 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62CDD6E6-9C47-462F-A7D1-88374DBBBFD8}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>209</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/data/Matriz_Seguimiento_Hallazgos.xlsx
+++ b/data/Matriz_Seguimiento_Hallazgos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Dashboard-Auditoria/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="645" documentId="8_{B9D78422-FDFF-47F2-8818-479A70B2C122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD3ADEAF-AA1A-4BD0-A6CE-3C2A65B9F1D3}"/>
+  <xr:revisionPtr revIDLastSave="649" documentId="8_{B9D78422-FDFF-47F2-8818-479A70B2C122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4CD6886-50A6-40E3-A932-647951E02FB5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -735,7 +735,7 @@
     <t>HASEG-24</t>
   </si>
   <si>
-    <t>Acción de mejora</t>
+    <t>Acción de Mejora</t>
   </si>
 </sst>
 </file>
@@ -999,63 +999,65 @@
   <dxfs count="73">
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF002060"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1852,47 +1854,6 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -2412,25 +2373,29 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2466,31 +2431,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3765,6 +3705,66 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -3783,84 +3783,81 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5BA7D11D-A526-4CEA-9DF8-80ED50D1CBD9}" name="Tabla3" displayName="Tabla3" ref="A1:AG13" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" tableBorderDxfId="35">
-  <autoFilter ref="A1:AG13" xr:uid="{5BA7D11D-A526-4CEA-9DF8-80ED50D1CBD9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5BA7D11D-A526-4CEA-9DF8-80ED50D1CBD9}" name="Tabla3" displayName="Tabla3" ref="A1:AG13" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37" tableBorderDxfId="36">
   <tableColumns count="33">
-    <tableColumn id="1" xr3:uid="{38023AA5-9776-4E80-A951-BE0FE68F1101}" name="Código Hallazgo" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{883B5642-97A6-4B67-A91F-312BB25E116A}" name="Fecha de Detección" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{C0E29A75-6D52-44C1-BBC8-1D0D9854730F}" name="Auditoría" dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{F8A3A88E-425E-4914-B771-61B543B87499}" name="Proceso" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{4115E30F-D80C-45FD-BBCE-3C3D007A45F0}" name="Subproceso" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{D5E799E7-238C-4410-8180-2F23404C38C5}" name="Responsable del Proceso" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{EF5F4C2C-D1C7-44F0-A107-641607336071}" name="Criterio Incumplido" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{F98540B2-06C0-4AB3-A036-DA30F86A9127}" name="Descripción del Hallazgo" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{7488B0F2-484A-4D7A-806A-B20AD5A4B44B}" name="Evidencia" dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{3046F0F7-5132-4A53-A672-1A0D51F6FD90}" name="Causa Raíz" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{51F65AE4-A931-4F03-9144-11BB7E1BA7EC}" name="Riesgos Asociados" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{DEAD9D0A-B936-416F-A091-B28F8DC890CA}" name="Tipo de Acción" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{8C244D88-600C-4C82-BC90-B9A59CFC691C}" name="Acción Correctiva" dataDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{DE25F41D-7D67-47E8-BB59-37A2E153EEB2}" name="Avance" dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{97EE2963-728C-4A52-A616-D5ABCB743209}" name="Responsable de la Acción" dataDxfId="20"/>
-    <tableColumn id="16" xr3:uid="{093911F5-09A4-453E-8292-E386A79C9C1D}" name="Área Responsable" dataDxfId="19"/>
-    <tableColumn id="17" xr3:uid="{DD857392-716E-4350-AE9B-2A43A13A5903}" name="Fecha Compromiso" dataDxfId="18"/>
-    <tableColumn id="18" xr3:uid="{1F28FB8B-3090-4702-AC1B-D1B5EA0CA13F}" name="Evidencia Esperada" dataDxfId="17"/>
-    <tableColumn id="19" xr3:uid="{D64795B7-F5AF-4717-BF92-0B8A45C7B89C}" name="Indicador de Cumplimiento" dataDxfId="16"/>
-    <tableColumn id="20" xr3:uid="{9280B508-D669-4CE9-A7D9-2F6D29B1724B}" name="Estado Automático" dataDxfId="15"/>
-    <tableColumn id="21" xr3:uid="{A6E3D81D-F7AE-4126-BAC2-068953DF2A77}" name="% Avance" dataDxfId="14"/>
-    <tableColumn id="22" xr3:uid="{83E6ABB0-426C-477B-901F-15705ACCE8EA}" name="Fecha Último Seguimiento" dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{F01F5465-D84D-4303-B442-EEF87F5FE407}" name="Observaciones de Seguimiento" dataDxfId="12"/>
-    <tableColumn id="24" xr3:uid="{FD269743-574B-4863-B455-390ACA96A5DE}" name="Escalado a Dirección" dataDxfId="11"/>
-    <tableColumn id="25" xr3:uid="{2E7ACEE0-5BD8-4436-B3AE-0157D22A3C8B}" name="Fecha de Escalamiento" dataDxfId="10"/>
-    <tableColumn id="26" xr3:uid="{61668FD7-E523-4D93-8EF7-63F3BCC15C61}" name="Fecha Implementación Real" dataDxfId="9"/>
-    <tableColumn id="27" xr3:uid="{40ABE0DD-161B-40D2-BC22-91747FB660E9}" name="Tipo de Validación" dataDxfId="8"/>
-    <tableColumn id="28" xr3:uid="{63735BCB-A0AD-4E66-B6EF-82CD0E5C8017}" name="Resultado de Validación" dataDxfId="7"/>
-    <tableColumn id="29" xr3:uid="{D137839B-0857-4CB3-B34D-0F30B28A8620}" name="Auditor que Valida" dataDxfId="6"/>
-    <tableColumn id="30" xr3:uid="{31624A5B-76AA-4C9E-8DF7-1BE589EC1D2B}" name="Fecha Cierre Oficial" dataDxfId="5"/>
-    <tableColumn id="31" xr3:uid="{21402088-000E-4EE6-B3CF-1172741519CA}" name="Reincidencia" dataDxfId="4"/>
-    <tableColumn id="32" xr3:uid="{7D71CFD1-9D53-4496-A1F8-E2B7ED050B67}" name="Impacto Mitigado" dataDxfId="3"/>
-    <tableColumn id="33" xr3:uid="{30C54FB7-6AE1-410A-B899-BC22AC520A10}" name="Comentarios de Cierre" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{38023AA5-9776-4E80-A951-BE0FE68F1101}" name="Código Hallazgo" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{883B5642-97A6-4B67-A91F-312BB25E116A}" name="Fecha de Detección" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{C0E29A75-6D52-44C1-BBC8-1D0D9854730F}" name="Auditoría" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{F8A3A88E-425E-4914-B771-61B543B87499}" name="Proceso" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{4115E30F-D80C-45FD-BBCE-3C3D007A45F0}" name="Subproceso" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{D5E799E7-238C-4410-8180-2F23404C38C5}" name="Responsable del Proceso" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{EF5F4C2C-D1C7-44F0-A107-641607336071}" name="Criterio Incumplido" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{F98540B2-06C0-4AB3-A036-DA30F86A9127}" name="Descripción del Hallazgo" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{7488B0F2-484A-4D7A-806A-B20AD5A4B44B}" name="Evidencia" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{3046F0F7-5132-4A53-A672-1A0D51F6FD90}" name="Causa Raíz" dataDxfId="26"/>
+    <tableColumn id="11" xr3:uid="{51F65AE4-A931-4F03-9144-11BB7E1BA7EC}" name="Riesgos Asociados" dataDxfId="25"/>
+    <tableColumn id="12" xr3:uid="{DEAD9D0A-B936-416F-A091-B28F8DC890CA}" name="Tipo de Acción" dataDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{8C244D88-600C-4C82-BC90-B9A59CFC691C}" name="Acción Correctiva" dataDxfId="24"/>
+    <tableColumn id="14" xr3:uid="{DE25F41D-7D67-47E8-BB59-37A2E153EEB2}" name="Avance" dataDxfId="23"/>
+    <tableColumn id="15" xr3:uid="{97EE2963-728C-4A52-A616-D5ABCB743209}" name="Responsable de la Acción" dataDxfId="22"/>
+    <tableColumn id="16" xr3:uid="{093911F5-09A4-453E-8292-E386A79C9C1D}" name="Área Responsable" dataDxfId="21"/>
+    <tableColumn id="17" xr3:uid="{DD857392-716E-4350-AE9B-2A43A13A5903}" name="Fecha Compromiso" dataDxfId="20"/>
+    <tableColumn id="18" xr3:uid="{1F28FB8B-3090-4702-AC1B-D1B5EA0CA13F}" name="Evidencia Esperada" dataDxfId="19"/>
+    <tableColumn id="19" xr3:uid="{D64795B7-F5AF-4717-BF92-0B8A45C7B89C}" name="Indicador de Cumplimiento" dataDxfId="18"/>
+    <tableColumn id="20" xr3:uid="{9280B508-D669-4CE9-A7D9-2F6D29B1724B}" name="Estado Automático" dataDxfId="17"/>
+    <tableColumn id="21" xr3:uid="{A6E3D81D-F7AE-4126-BAC2-068953DF2A77}" name="% Avance" dataDxfId="16"/>
+    <tableColumn id="22" xr3:uid="{83E6ABB0-426C-477B-901F-15705ACCE8EA}" name="Fecha Último Seguimiento" dataDxfId="15"/>
+    <tableColumn id="23" xr3:uid="{F01F5465-D84D-4303-B442-EEF87F5FE407}" name="Observaciones de Seguimiento" dataDxfId="14"/>
+    <tableColumn id="24" xr3:uid="{FD269743-574B-4863-B455-390ACA96A5DE}" name="Escalado a Dirección" dataDxfId="13"/>
+    <tableColumn id="25" xr3:uid="{2E7ACEE0-5BD8-4436-B3AE-0157D22A3C8B}" name="Fecha de Escalamiento" dataDxfId="12"/>
+    <tableColumn id="26" xr3:uid="{61668FD7-E523-4D93-8EF7-63F3BCC15C61}" name="Fecha Implementación Real" dataDxfId="11"/>
+    <tableColumn id="27" xr3:uid="{40ABE0DD-161B-40D2-BC22-91747FB660E9}" name="Tipo de Validación" dataDxfId="10"/>
+    <tableColumn id="28" xr3:uid="{63735BCB-A0AD-4E66-B6EF-82CD0E5C8017}" name="Resultado de Validación" dataDxfId="9"/>
+    <tableColumn id="29" xr3:uid="{D137839B-0857-4CB3-B34D-0F30B28A8620}" name="Auditor que Valida" dataDxfId="8"/>
+    <tableColumn id="30" xr3:uid="{31624A5B-76AA-4C9E-8DF7-1BE589EC1D2B}" name="Fecha Cierre Oficial" dataDxfId="7"/>
+    <tableColumn id="31" xr3:uid="{21402088-000E-4EE6-B3CF-1172741519CA}" name="Reincidencia" dataDxfId="6"/>
+    <tableColumn id="32" xr3:uid="{7D71CFD1-9D53-4496-A1F8-E2B7ED050B67}" name="Impacto Mitigado" dataDxfId="5"/>
+    <tableColumn id="33" xr3:uid="{30C54FB7-6AE1-410A-B899-BC22AC520A10}" name="Comentarios de Cierre" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{22FB0005-8F63-4CE1-938E-B216418660F6}" name="Tabla1" displayName="Tabla1" ref="A1:AE25" totalsRowShown="0" headerRowDxfId="39" dataDxfId="40" tableBorderDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{22FB0005-8F63-4CE1-938E-B216418660F6}" name="Tabla1" displayName="Tabla1" ref="A1:AE25" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71" tableBorderDxfId="70">
   <autoFilter ref="A1:AE25" xr:uid="{22FB0005-8F63-4CE1-938E-B216418660F6}"/>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{C445E1C6-F781-4A05-A8DB-BB9CC1F5A338}" name="Código Hallazgo" dataDxfId="71"/>
-    <tableColumn id="2" xr3:uid="{90EAE778-D38B-49EF-B34D-315F9A7A5A27}" name="Fecha de Cierre" dataDxfId="70"/>
-    <tableColumn id="3" xr3:uid="{C0D5052E-084A-4422-8247-58D55C619725}" name="Auditoría" dataDxfId="69"/>
-    <tableColumn id="4" xr3:uid="{5D3256A2-BA02-44EC-95EB-2C06CE880405}" name="Proceso" dataDxfId="68"/>
-    <tableColumn id="5" xr3:uid="{893633F6-D257-4D10-8927-3D3A728B911A}" name="Subproceso" dataDxfId="67"/>
-    <tableColumn id="6" xr3:uid="{1ACBDFC4-A8D2-4E4E-B0A8-F320C769D36F}" name="Responsable del Proceso" dataDxfId="66"/>
-    <tableColumn id="7" xr3:uid="{458512AC-6A36-47C9-AC84-D62D31450CAA}" name="Criticidad" dataDxfId="65"/>
-    <tableColumn id="8" xr3:uid="{F2E3079A-A9A6-49A5-A02F-AF83100B696B}" name="Criterio Incumplido" dataDxfId="64"/>
-    <tableColumn id="9" xr3:uid="{42F33B5C-BC64-4551-83E2-5C33C69EC227}" name="Descripción del Hallazgo" dataDxfId="63"/>
-    <tableColumn id="10" xr3:uid="{9CF403EB-8414-4F4C-B74F-0679F4979A1C}" name="Riesgos Asociados" dataDxfId="62"/>
-    <tableColumn id="11" xr3:uid="{F4506974-B5EF-4B33-A978-8D4F503123A7}" name="Tipo de Acción" dataDxfId="61"/>
-    <tableColumn id="12" xr3:uid="{2A3BC71B-97A7-4F6A-A427-E20FA980B65F}" name="Acciones / Actividades" dataDxfId="60"/>
-    <tableColumn id="13" xr3:uid="{2CDD1D9D-33E2-44C4-94C7-280236B55BA8}" name="Responsable de la Acción" dataDxfId="59"/>
-    <tableColumn id="14" xr3:uid="{29E6C5DC-7EA4-49BD-9F29-57DA71718F20}" name="Área Responsable" dataDxfId="58"/>
-    <tableColumn id="15" xr3:uid="{2B6D1608-654F-4177-832E-561B75E0AA26}" name="Fecha Compromiso" dataDxfId="57"/>
-    <tableColumn id="16" xr3:uid="{1ED50EB0-1860-4E22-9EF1-F93210496EDD}" name="Evidencia Esperada" dataDxfId="56"/>
-    <tableColumn id="17" xr3:uid="{8F0EB8AC-437B-4325-8ABA-666909D9B5F8}" name="Indicador de Cumplimiento" dataDxfId="55"/>
-    <tableColumn id="18" xr3:uid="{C7EEC45E-ECAD-4B56-93C0-4B5AE924CD8E}" name="Estado Automático" dataDxfId="54">
-      <calculatedColumnFormula>IF(AND(O2&lt;TODAY(),R2&lt;&gt;"Cerrado"),"Vencido",R2)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="19" xr3:uid="{2722D635-9314-4F49-B035-B9A724C5210A}" name="% Avance" dataDxfId="53"/>
-    <tableColumn id="20" xr3:uid="{28A730BA-4EA7-49DF-9399-6E00D5292AB2}" name="Fecha Último Seguimiento" dataDxfId="52"/>
-    <tableColumn id="21" xr3:uid="{F70EE4EC-D6C1-4265-B078-19D148BC2906}" name="Observaciones de Seguimiento" dataDxfId="51"/>
-    <tableColumn id="22" xr3:uid="{C964C47F-52C9-426B-B6E5-974094EDB9DE}" name="Escalado a Dirección" dataDxfId="50"/>
-    <tableColumn id="23" xr3:uid="{36A8271D-7EA2-487A-A00A-D3AD91C530B1}" name="Fecha de Escalamiento" dataDxfId="49"/>
-    <tableColumn id="24" xr3:uid="{AB72CFF0-E4FD-4906-9E3E-23B7E97C9D47}" name="Fecha Implementación Real" dataDxfId="48"/>
-    <tableColumn id="25" xr3:uid="{2E3BE42A-F44C-4E50-AF37-498FDB63B8C9}" name="Tipo de Validación" dataDxfId="47"/>
-    <tableColumn id="26" xr3:uid="{F12F1141-56CD-411F-8B57-54F18AE19AB1}" name="Resultado de Validación" dataDxfId="46"/>
-    <tableColumn id="27" xr3:uid="{B53A8C3D-2477-4D08-BBF6-39ED220F441F}" name="Auditor que Valida" dataDxfId="45"/>
-    <tableColumn id="28" xr3:uid="{02AE6B85-C8E3-458F-99DE-6C3A7C997538}" name="Fecha Cierre Oficial" dataDxfId="44"/>
-    <tableColumn id="29" xr3:uid="{0280F784-8789-4BD2-8B63-2885D043177E}" name="Reincidencia" dataDxfId="43"/>
-    <tableColumn id="30" xr3:uid="{B33911EB-ED81-48C2-8376-B92BC2D7744C}" name="Impacto Mitigado" dataDxfId="42"/>
-    <tableColumn id="31" xr3:uid="{8ACAEBDD-C331-4809-91C4-834E371130EB}" name="Comentarios de Cierre" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{C445E1C6-F781-4A05-A8DB-BB9CC1F5A338}" name="Código Hallazgo" dataDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{90EAE778-D38B-49EF-B34D-315F9A7A5A27}" name="Fecha de Cierre" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{C0D5052E-084A-4422-8247-58D55C619725}" name="Auditoría" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{5D3256A2-BA02-44EC-95EB-2C06CE880405}" name="Proceso" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{893633F6-D257-4D10-8927-3D3A728B911A}" name="Subproceso" dataDxfId="65"/>
+    <tableColumn id="6" xr3:uid="{1ACBDFC4-A8D2-4E4E-B0A8-F320C769D36F}" name="Responsable del Proceso" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{458512AC-6A36-47C9-AC84-D62D31450CAA}" name="Criticidad" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{F2E3079A-A9A6-49A5-A02F-AF83100B696B}" name="Criterio Incumplido" dataDxfId="62"/>
+    <tableColumn id="9" xr3:uid="{42F33B5C-BC64-4551-83E2-5C33C69EC227}" name="Descripción del Hallazgo" dataDxfId="61"/>
+    <tableColumn id="10" xr3:uid="{9CF403EB-8414-4F4C-B74F-0679F4979A1C}" name="Riesgos Asociados" dataDxfId="60"/>
+    <tableColumn id="11" xr3:uid="{F4506974-B5EF-4B33-A978-8D4F503123A7}" name="Tipo de Acción" dataDxfId="59"/>
+    <tableColumn id="12" xr3:uid="{2A3BC71B-97A7-4F6A-A427-E20FA980B65F}" name="Acciones / Actividades" dataDxfId="58"/>
+    <tableColumn id="13" xr3:uid="{2CDD1D9D-33E2-44C4-94C7-280236B55BA8}" name="Responsable de la Acción" dataDxfId="57"/>
+    <tableColumn id="14" xr3:uid="{29E6C5DC-7EA4-49BD-9F29-57DA71718F20}" name="Área Responsable" dataDxfId="56"/>
+    <tableColumn id="15" xr3:uid="{2B6D1608-654F-4177-832E-561B75E0AA26}" name="Fecha Compromiso" dataDxfId="55"/>
+    <tableColumn id="16" xr3:uid="{1ED50EB0-1860-4E22-9EF1-F93210496EDD}" name="Evidencia Esperada" dataDxfId="54"/>
+    <tableColumn id="17" xr3:uid="{8F0EB8AC-437B-4325-8ABA-666909D9B5F8}" name="Indicador de Cumplimiento" dataDxfId="53"/>
+    <tableColumn id="18" xr3:uid="{C7EEC45E-ECAD-4B56-93C0-4B5AE924CD8E}" name="Estado Automático" dataDxfId="52"/>
+    <tableColumn id="19" xr3:uid="{2722D635-9314-4F49-B035-B9A724C5210A}" name="% Avance" dataDxfId="51"/>
+    <tableColumn id="20" xr3:uid="{28A730BA-4EA7-49DF-9399-6E00D5292AB2}" name="Fecha Último Seguimiento" dataDxfId="50"/>
+    <tableColumn id="21" xr3:uid="{F70EE4EC-D6C1-4265-B078-19D148BC2906}" name="Observaciones de Seguimiento" dataDxfId="49"/>
+    <tableColumn id="22" xr3:uid="{C964C47F-52C9-426B-B6E5-974094EDB9DE}" name="Escalado a Dirección" dataDxfId="48"/>
+    <tableColumn id="23" xr3:uid="{36A8271D-7EA2-487A-A00A-D3AD91C530B1}" name="Fecha de Escalamiento" dataDxfId="47"/>
+    <tableColumn id="24" xr3:uid="{AB72CFF0-E4FD-4906-9E3E-23B7E97C9D47}" name="Fecha Implementación Real" dataDxfId="46"/>
+    <tableColumn id="25" xr3:uid="{2E3BE42A-F44C-4E50-AF37-498FDB63B8C9}" name="Tipo de Validación" dataDxfId="45"/>
+    <tableColumn id="26" xr3:uid="{F12F1141-56CD-411F-8B57-54F18AE19AB1}" name="Resultado de Validación" dataDxfId="44"/>
+    <tableColumn id="27" xr3:uid="{B53A8C3D-2477-4D08-BBF6-39ED220F441F}" name="Auditor que Valida" dataDxfId="43"/>
+    <tableColumn id="28" xr3:uid="{02AE6B85-C8E3-458F-99DE-6C3A7C997538}" name="Fecha Cierre Oficial" dataDxfId="42"/>
+    <tableColumn id="29" xr3:uid="{0280F784-8789-4BD2-8B63-2885D043177E}" name="Reincidencia" dataDxfId="41"/>
+    <tableColumn id="30" xr3:uid="{B33911EB-ED81-48C2-8376-B92BC2D7744C}" name="Impacto Mitigado" dataDxfId="40"/>
+    <tableColumn id="31" xr3:uid="{8ACAEBDD-C331-4809-91C4-834E371130EB}" name="Comentarios de Cierre" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4189,7 +4186,7 @@
     <col min="33" max="33" width="27" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" ht="15" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -4530,7 +4527,7 @@
       <c r="AF5" s="3"/>
       <c r="AG5" s="27"/>
     </row>
-    <row r="6" spans="1:33" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A6" s="31" t="s">
         <v>176</v>
       </c>
@@ -4648,7 +4645,7 @@
       <c r="AF7" s="3"/>
       <c r="AG7" s="27"/>
     </row>
-    <row r="8" spans="1:33" ht="66" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A8" s="31" t="s">
         <v>178</v>
       </c>
@@ -4766,7 +4763,7 @@
       <c r="AF9" s="3"/>
       <c r="AG9" s="27"/>
     </row>
-    <row r="10" spans="1:33" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A10" s="31" t="s">
         <v>180</v>
       </c>
@@ -4943,7 +4940,7 @@
       <c r="AF12" s="3"/>
       <c r="AG12" s="27"/>
     </row>
-    <row r="13" spans="1:33" ht="66" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A13" s="32" t="s">
         <v>182</v>
       </c>
@@ -4973,7 +4970,7 @@
       </c>
       <c r="J13" s="20"/>
       <c r="K13" s="20"/>
-      <c r="L13" s="21" t="s">
+      <c r="L13" s="5" t="s">
         <v>207</v>
       </c>
       <c r="M13" s="21">
@@ -5111,7 +5108,7 @@
     <col min="31" max="31" width="27" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="15" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -5556,10 +5553,7 @@
         <v>125</v>
       </c>
       <c r="Q8" s="5"/>
-      <c r="R8" s="5">
-        <f ca="1">IF(AND(O8&lt;TODAY(),R8&lt;&gt;"Cerrado"),"Vencido",R8)</f>
-        <v>0</v>
-      </c>
+      <c r="R8" s="5"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
@@ -5578,7 +5572,7 @@
       <c r="AD8" s="5"/>
       <c r="AE8" s="26"/>
     </row>
-    <row r="9" spans="1:31" ht="198" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
         <v>190</v>
       </c>
@@ -5622,10 +5616,7 @@
         <v>125</v>
       </c>
       <c r="Q9" s="3"/>
-      <c r="R9" s="3" t="str">
-        <f t="shared" ref="R9:R25" ca="1" si="0">IF(AND(O9&lt;TODAY(),R9&lt;&gt;"Cerrado"),"Vencido",R9)</f>
-        <v/>
-      </c>
+      <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
@@ -5640,7 +5631,7 @@
       <c r="AD9" s="3"/>
       <c r="AE9" s="27"/>
     </row>
-    <row r="10" spans="1:31" ht="198" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
         <v>191</v>
       </c>
@@ -5684,10 +5675,7 @@
         <v>125</v>
       </c>
       <c r="Q10" s="3"/>
-      <c r="R10" s="3" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -5746,10 +5734,7 @@
         <v>125</v>
       </c>
       <c r="Q11" s="3"/>
-      <c r="R11" s="3" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
@@ -5802,10 +5787,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
-      <c r="R12" s="3" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
@@ -5858,10 +5840,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
-      <c r="R13" s="3" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
@@ -5914,10 +5893,7 @@
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
-      <c r="R14" s="3" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
@@ -5970,10 +5946,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
-      <c r="R15" s="3" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R15" s="3"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
@@ -6026,10 +5999,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-      <c r="R16" s="3" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -6082,10 +6052,7 @@
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
-      <c r="R17" s="3" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R17" s="3"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
@@ -6138,10 +6105,7 @@
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
-      <c r="R18" s="3" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R18" s="3"/>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
@@ -6194,10 +6158,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-      <c r="R19" s="3" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
@@ -6250,10 +6211,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
-      <c r="R20" s="3" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R20" s="3"/>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
@@ -6306,10 +6264,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
-      <c r="R21" s="3" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R21" s="3"/>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
@@ -6362,10 +6317,7 @@
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
-      <c r="R22" s="3" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R22" s="3"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
@@ -6416,10 +6368,7 @@
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
-      <c r="R23" s="3" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
@@ -6472,10 +6421,7 @@
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
-      <c r="R24" s="3" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R24" s="3"/>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
@@ -6528,10 +6474,7 @@
       <c r="O25" s="20"/>
       <c r="P25" s="20"/>
       <c r="Q25" s="20"/>
-      <c r="R25" s="20" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
+      <c r="R25" s="20"/>
       <c r="S25" s="20"/>
       <c r="T25" s="20"/>
       <c r="U25" s="20"/>
@@ -6549,17 +6492,17 @@
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="38" priority="3" operator="containsText" text="Bajo">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Bajo">
       <formula>NOT(ISERROR(SEARCH("Bajo",G1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="4" operator="containsText" text="Medio">
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="Medio">
       <formula>NOT(ISERROR(SEARCH("Medio",G1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="5" operator="containsText" text="Alto">
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="Alto">
       <formula>NOT(ISERROR(SEARCH("Alto",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <dataValidations disablePrompts="1" count="5">
     <dataValidation type="list" allowBlank="1" sqref="R8:R25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Abierto,En proceso,Cerrado"</formula1>
     </dataValidation>
@@ -6601,18 +6544,18 @@
       <c r="A3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="str">
-        <f ca="1">COUNTIF('Base Hallazgos Aseguramiento'!R:R,"Cerrado")/COUNTA('Base Hallazgos Aseguramiento'!C:C)</f>
-        <v/>
+      <c r="B3">
+        <f>COUNTIF('Base Hallazgos Aseguramiento'!R:R,"Cerrado")/COUNTA('Base Hallazgos Aseguramiento'!C:C)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" t="str">
-        <f ca="1">COUNTIF('Base Hallazgos Aseguramiento'!R:R,"Vencido")/COUNTA('Base Hallazgos Aseguramiento'!C:C)</f>
-        <v/>
+      <c r="B4">
+        <f>COUNTIF('Base Hallazgos Aseguramiento'!R:R,"Vencido")/COUNTA('Base Hallazgos Aseguramiento'!C:C)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/Matriz_Seguimiento_Hallazgos.xlsx
+++ b/data/Matriz_Seguimiento_Hallazgos.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="649" documentId="8_{B9D78422-FDFF-47F2-8818-479A70B2C122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4CD6886-50A6-40E3-A932-647951E02FB5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base Hallazgos SIG" sheetId="4" r:id="rId1"/>
@@ -998,6 +998,1009 @@
   </cellStyles>
   <dxfs count="73">
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1039,27 +2042,6 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1087,7 +2069,9 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1238,6 +2222,154 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1249,9 +2381,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1853,7 +2983,212 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -2343,1341 +3678,6 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF002060"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -3783,81 +3783,81 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5BA7D11D-A526-4CEA-9DF8-80ED50D1CBD9}" name="Tabla3" displayName="Tabla3" ref="A1:AG13" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37" tableBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5BA7D11D-A526-4CEA-9DF8-80ED50D1CBD9}" name="Tabla3" displayName="Tabla3" ref="A1:AG13" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71" tableBorderDxfId="70">
   <tableColumns count="33">
-    <tableColumn id="1" xr3:uid="{38023AA5-9776-4E80-A951-BE0FE68F1101}" name="Código Hallazgo" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{883B5642-97A6-4B67-A91F-312BB25E116A}" name="Fecha de Detección" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{C0E29A75-6D52-44C1-BBC8-1D0D9854730F}" name="Auditoría" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{F8A3A88E-425E-4914-B771-61B543B87499}" name="Proceso" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{4115E30F-D80C-45FD-BBCE-3C3D007A45F0}" name="Subproceso" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{D5E799E7-238C-4410-8180-2F23404C38C5}" name="Responsable del Proceso" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{EF5F4C2C-D1C7-44F0-A107-641607336071}" name="Criterio Incumplido" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{F98540B2-06C0-4AB3-A036-DA30F86A9127}" name="Descripción del Hallazgo" dataDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{7488B0F2-484A-4D7A-806A-B20AD5A4B44B}" name="Evidencia" dataDxfId="27"/>
-    <tableColumn id="10" xr3:uid="{3046F0F7-5132-4A53-A672-1A0D51F6FD90}" name="Causa Raíz" dataDxfId="26"/>
-    <tableColumn id="11" xr3:uid="{51F65AE4-A931-4F03-9144-11BB7E1BA7EC}" name="Riesgos Asociados" dataDxfId="25"/>
-    <tableColumn id="12" xr3:uid="{DEAD9D0A-B936-416F-A091-B28F8DC890CA}" name="Tipo de Acción" dataDxfId="0"/>
-    <tableColumn id="13" xr3:uid="{8C244D88-600C-4C82-BC90-B9A59CFC691C}" name="Acción Correctiva" dataDxfId="24"/>
-    <tableColumn id="14" xr3:uid="{DE25F41D-7D67-47E8-BB59-37A2E153EEB2}" name="Avance" dataDxfId="23"/>
-    <tableColumn id="15" xr3:uid="{97EE2963-728C-4A52-A616-D5ABCB743209}" name="Responsable de la Acción" dataDxfId="22"/>
-    <tableColumn id="16" xr3:uid="{093911F5-09A4-453E-8292-E386A79C9C1D}" name="Área Responsable" dataDxfId="21"/>
-    <tableColumn id="17" xr3:uid="{DD857392-716E-4350-AE9B-2A43A13A5903}" name="Fecha Compromiso" dataDxfId="20"/>
-    <tableColumn id="18" xr3:uid="{1F28FB8B-3090-4702-AC1B-D1B5EA0CA13F}" name="Evidencia Esperada" dataDxfId="19"/>
-    <tableColumn id="19" xr3:uid="{D64795B7-F5AF-4717-BF92-0B8A45C7B89C}" name="Indicador de Cumplimiento" dataDxfId="18"/>
-    <tableColumn id="20" xr3:uid="{9280B508-D669-4CE9-A7D9-2F6D29B1724B}" name="Estado Automático" dataDxfId="17"/>
-    <tableColumn id="21" xr3:uid="{A6E3D81D-F7AE-4126-BAC2-068953DF2A77}" name="% Avance" dataDxfId="16"/>
-    <tableColumn id="22" xr3:uid="{83E6ABB0-426C-477B-901F-15705ACCE8EA}" name="Fecha Último Seguimiento" dataDxfId="15"/>
-    <tableColumn id="23" xr3:uid="{F01F5465-D84D-4303-B442-EEF87F5FE407}" name="Observaciones de Seguimiento" dataDxfId="14"/>
-    <tableColumn id="24" xr3:uid="{FD269743-574B-4863-B455-390ACA96A5DE}" name="Escalado a Dirección" dataDxfId="13"/>
-    <tableColumn id="25" xr3:uid="{2E7ACEE0-5BD8-4436-B3AE-0157D22A3C8B}" name="Fecha de Escalamiento" dataDxfId="12"/>
-    <tableColumn id="26" xr3:uid="{61668FD7-E523-4D93-8EF7-63F3BCC15C61}" name="Fecha Implementación Real" dataDxfId="11"/>
-    <tableColumn id="27" xr3:uid="{40ABE0DD-161B-40D2-BC22-91747FB660E9}" name="Tipo de Validación" dataDxfId="10"/>
-    <tableColumn id="28" xr3:uid="{63735BCB-A0AD-4E66-B6EF-82CD0E5C8017}" name="Resultado de Validación" dataDxfId="9"/>
-    <tableColumn id="29" xr3:uid="{D137839B-0857-4CB3-B34D-0F30B28A8620}" name="Auditor que Valida" dataDxfId="8"/>
-    <tableColumn id="30" xr3:uid="{31624A5B-76AA-4C9E-8DF7-1BE589EC1D2B}" name="Fecha Cierre Oficial" dataDxfId="7"/>
-    <tableColumn id="31" xr3:uid="{21402088-000E-4EE6-B3CF-1172741519CA}" name="Reincidencia" dataDxfId="6"/>
-    <tableColumn id="32" xr3:uid="{7D71CFD1-9D53-4496-A1F8-E2B7ED050B67}" name="Impacto Mitigado" dataDxfId="5"/>
-    <tableColumn id="33" xr3:uid="{30C54FB7-6AE1-410A-B899-BC22AC520A10}" name="Comentarios de Cierre" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{38023AA5-9776-4E80-A951-BE0FE68F1101}" name="Código Hallazgo" dataDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{883B5642-97A6-4B67-A91F-312BB25E116A}" name="Fecha de Detección" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{C0E29A75-6D52-44C1-BBC8-1D0D9854730F}" name="Auditoría" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{F8A3A88E-425E-4914-B771-61B543B87499}" name="Proceso" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{4115E30F-D80C-45FD-BBCE-3C3D007A45F0}" name="Subproceso" dataDxfId="65"/>
+    <tableColumn id="6" xr3:uid="{D5E799E7-238C-4410-8180-2F23404C38C5}" name="Responsable del Proceso" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{EF5F4C2C-D1C7-44F0-A107-641607336071}" name="Criterio Incumplido" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{F98540B2-06C0-4AB3-A036-DA30F86A9127}" name="Descripción del Hallazgo" dataDxfId="62"/>
+    <tableColumn id="9" xr3:uid="{7488B0F2-484A-4D7A-806A-B20AD5A4B44B}" name="Evidencia" dataDxfId="61"/>
+    <tableColumn id="10" xr3:uid="{3046F0F7-5132-4A53-A672-1A0D51F6FD90}" name="Causa Raíz" dataDxfId="60"/>
+    <tableColumn id="11" xr3:uid="{51F65AE4-A931-4F03-9144-11BB7E1BA7EC}" name="Riesgos Asociados" dataDxfId="59"/>
+    <tableColumn id="12" xr3:uid="{DEAD9D0A-B936-416F-A091-B28F8DC890CA}" name="Tipo de Acción" dataDxfId="58"/>
+    <tableColumn id="13" xr3:uid="{8C244D88-600C-4C82-BC90-B9A59CFC691C}" name="Acción Correctiva" dataDxfId="57"/>
+    <tableColumn id="14" xr3:uid="{DE25F41D-7D67-47E8-BB59-37A2E153EEB2}" name="Avance" dataDxfId="56"/>
+    <tableColumn id="15" xr3:uid="{97EE2963-728C-4A52-A616-D5ABCB743209}" name="Responsable de la Acción" dataDxfId="55"/>
+    <tableColumn id="16" xr3:uid="{093911F5-09A4-453E-8292-E386A79C9C1D}" name="Área Responsable" dataDxfId="54"/>
+    <tableColumn id="17" xr3:uid="{DD857392-716E-4350-AE9B-2A43A13A5903}" name="Fecha Compromiso" dataDxfId="53"/>
+    <tableColumn id="18" xr3:uid="{1F28FB8B-3090-4702-AC1B-D1B5EA0CA13F}" name="Evidencia Esperada" dataDxfId="52"/>
+    <tableColumn id="19" xr3:uid="{D64795B7-F5AF-4717-BF92-0B8A45C7B89C}" name="Indicador de Cumplimiento" dataDxfId="51"/>
+    <tableColumn id="20" xr3:uid="{9280B508-D669-4CE9-A7D9-2F6D29B1724B}" name="Estado Automático" dataDxfId="50"/>
+    <tableColumn id="21" xr3:uid="{A6E3D81D-F7AE-4126-BAC2-068953DF2A77}" name="% Avance" dataDxfId="49"/>
+    <tableColumn id="22" xr3:uid="{83E6ABB0-426C-477B-901F-15705ACCE8EA}" name="Fecha Último Seguimiento" dataDxfId="48"/>
+    <tableColumn id="23" xr3:uid="{F01F5465-D84D-4303-B442-EEF87F5FE407}" name="Observaciones de Seguimiento" dataDxfId="47"/>
+    <tableColumn id="24" xr3:uid="{FD269743-574B-4863-B455-390ACA96A5DE}" name="Escalado a Dirección" dataDxfId="46"/>
+    <tableColumn id="25" xr3:uid="{2E7ACEE0-5BD8-4436-B3AE-0157D22A3C8B}" name="Fecha de Escalamiento" dataDxfId="45"/>
+    <tableColumn id="26" xr3:uid="{61668FD7-E523-4D93-8EF7-63F3BCC15C61}" name="Fecha Implementación Real" dataDxfId="44"/>
+    <tableColumn id="27" xr3:uid="{40ABE0DD-161B-40D2-BC22-91747FB660E9}" name="Tipo de Validación" dataDxfId="43"/>
+    <tableColumn id="28" xr3:uid="{63735BCB-A0AD-4E66-B6EF-82CD0E5C8017}" name="Resultado de Validación" dataDxfId="42"/>
+    <tableColumn id="29" xr3:uid="{D137839B-0857-4CB3-B34D-0F30B28A8620}" name="Auditor que Valida" dataDxfId="41"/>
+    <tableColumn id="30" xr3:uid="{31624A5B-76AA-4C9E-8DF7-1BE589EC1D2B}" name="Fecha Cierre Oficial" dataDxfId="40"/>
+    <tableColumn id="31" xr3:uid="{21402088-000E-4EE6-B3CF-1172741519CA}" name="Reincidencia" dataDxfId="39"/>
+    <tableColumn id="32" xr3:uid="{7D71CFD1-9D53-4496-A1F8-E2B7ED050B67}" name="Impacto Mitigado" dataDxfId="38"/>
+    <tableColumn id="33" xr3:uid="{30C54FB7-6AE1-410A-B899-BC22AC520A10}" name="Comentarios de Cierre" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{22FB0005-8F63-4CE1-938E-B216418660F6}" name="Tabla1" displayName="Tabla1" ref="A1:AE25" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71" tableBorderDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{22FB0005-8F63-4CE1-938E-B216418660F6}" name="Tabla1" displayName="Tabla1" ref="A1:AE25" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35" tableBorderDxfId="34">
   <autoFilter ref="A1:AE25" xr:uid="{22FB0005-8F63-4CE1-938E-B216418660F6}"/>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{C445E1C6-F781-4A05-A8DB-BB9CC1F5A338}" name="Código Hallazgo" dataDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{90EAE778-D38B-49EF-B34D-315F9A7A5A27}" name="Fecha de Cierre" dataDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{C0D5052E-084A-4422-8247-58D55C619725}" name="Auditoría" dataDxfId="67"/>
-    <tableColumn id="4" xr3:uid="{5D3256A2-BA02-44EC-95EB-2C06CE880405}" name="Proceso" dataDxfId="66"/>
-    <tableColumn id="5" xr3:uid="{893633F6-D257-4D10-8927-3D3A728B911A}" name="Subproceso" dataDxfId="65"/>
-    <tableColumn id="6" xr3:uid="{1ACBDFC4-A8D2-4E4E-B0A8-F320C769D36F}" name="Responsable del Proceso" dataDxfId="64"/>
-    <tableColumn id="7" xr3:uid="{458512AC-6A36-47C9-AC84-D62D31450CAA}" name="Criticidad" dataDxfId="63"/>
-    <tableColumn id="8" xr3:uid="{F2E3079A-A9A6-49A5-A02F-AF83100B696B}" name="Criterio Incumplido" dataDxfId="62"/>
-    <tableColumn id="9" xr3:uid="{42F33B5C-BC64-4551-83E2-5C33C69EC227}" name="Descripción del Hallazgo" dataDxfId="61"/>
-    <tableColumn id="10" xr3:uid="{9CF403EB-8414-4F4C-B74F-0679F4979A1C}" name="Riesgos Asociados" dataDxfId="60"/>
-    <tableColumn id="11" xr3:uid="{F4506974-B5EF-4B33-A978-8D4F503123A7}" name="Tipo de Acción" dataDxfId="59"/>
-    <tableColumn id="12" xr3:uid="{2A3BC71B-97A7-4F6A-A427-E20FA980B65F}" name="Acciones / Actividades" dataDxfId="58"/>
-    <tableColumn id="13" xr3:uid="{2CDD1D9D-33E2-44C4-94C7-280236B55BA8}" name="Responsable de la Acción" dataDxfId="57"/>
-    <tableColumn id="14" xr3:uid="{29E6C5DC-7EA4-49BD-9F29-57DA71718F20}" name="Área Responsable" dataDxfId="56"/>
-    <tableColumn id="15" xr3:uid="{2B6D1608-654F-4177-832E-561B75E0AA26}" name="Fecha Compromiso" dataDxfId="55"/>
-    <tableColumn id="16" xr3:uid="{1ED50EB0-1860-4E22-9EF1-F93210496EDD}" name="Evidencia Esperada" dataDxfId="54"/>
-    <tableColumn id="17" xr3:uid="{8F0EB8AC-437B-4325-8ABA-666909D9B5F8}" name="Indicador de Cumplimiento" dataDxfId="53"/>
-    <tableColumn id="18" xr3:uid="{C7EEC45E-ECAD-4B56-93C0-4B5AE924CD8E}" name="Estado Automático" dataDxfId="52"/>
-    <tableColumn id="19" xr3:uid="{2722D635-9314-4F49-B035-B9A724C5210A}" name="% Avance" dataDxfId="51"/>
-    <tableColumn id="20" xr3:uid="{28A730BA-4EA7-49DF-9399-6E00D5292AB2}" name="Fecha Último Seguimiento" dataDxfId="50"/>
-    <tableColumn id="21" xr3:uid="{F70EE4EC-D6C1-4265-B078-19D148BC2906}" name="Observaciones de Seguimiento" dataDxfId="49"/>
-    <tableColumn id="22" xr3:uid="{C964C47F-52C9-426B-B6E5-974094EDB9DE}" name="Escalado a Dirección" dataDxfId="48"/>
-    <tableColumn id="23" xr3:uid="{36A8271D-7EA2-487A-A00A-D3AD91C530B1}" name="Fecha de Escalamiento" dataDxfId="47"/>
-    <tableColumn id="24" xr3:uid="{AB72CFF0-E4FD-4906-9E3E-23B7E97C9D47}" name="Fecha Implementación Real" dataDxfId="46"/>
-    <tableColumn id="25" xr3:uid="{2E3BE42A-F44C-4E50-AF37-498FDB63B8C9}" name="Tipo de Validación" dataDxfId="45"/>
-    <tableColumn id="26" xr3:uid="{F12F1141-56CD-411F-8B57-54F18AE19AB1}" name="Resultado de Validación" dataDxfId="44"/>
-    <tableColumn id="27" xr3:uid="{B53A8C3D-2477-4D08-BBF6-39ED220F441F}" name="Auditor que Valida" dataDxfId="43"/>
-    <tableColumn id="28" xr3:uid="{02AE6B85-C8E3-458F-99DE-6C3A7C997538}" name="Fecha Cierre Oficial" dataDxfId="42"/>
-    <tableColumn id="29" xr3:uid="{0280F784-8789-4BD2-8B63-2885D043177E}" name="Reincidencia" dataDxfId="41"/>
-    <tableColumn id="30" xr3:uid="{B33911EB-ED81-48C2-8376-B92BC2D7744C}" name="Impacto Mitigado" dataDxfId="40"/>
-    <tableColumn id="31" xr3:uid="{8ACAEBDD-C331-4809-91C4-834E371130EB}" name="Comentarios de Cierre" dataDxfId="39"/>
+    <tableColumn id="1" xr3:uid="{C445E1C6-F781-4A05-A8DB-BB9CC1F5A338}" name="Código Hallazgo" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{90EAE778-D38B-49EF-B34D-315F9A7A5A27}" name="Fecha de Cierre" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{C0D5052E-084A-4422-8247-58D55C619725}" name="Auditoría" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{5D3256A2-BA02-44EC-95EB-2C06CE880405}" name="Proceso" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{893633F6-D257-4D10-8927-3D3A728B911A}" name="Subproceso" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{1ACBDFC4-A8D2-4E4E-B0A8-F320C769D36F}" name="Responsable del Proceso" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{458512AC-6A36-47C9-AC84-D62D31450CAA}" name="Criticidad" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{F2E3079A-A9A6-49A5-A02F-AF83100B696B}" name="Criterio Incumplido" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{42F33B5C-BC64-4551-83E2-5C33C69EC227}" name="Descripción del Hallazgo" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{9CF403EB-8414-4F4C-B74F-0679F4979A1C}" name="Riesgos Asociados" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{F4506974-B5EF-4B33-A978-8D4F503123A7}" name="Tipo de Acción" dataDxfId="23"/>
+    <tableColumn id="12" xr3:uid="{2A3BC71B-97A7-4F6A-A427-E20FA980B65F}" name="Acciones / Actividades" dataDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{2CDD1D9D-33E2-44C4-94C7-280236B55BA8}" name="Responsable de la Acción" dataDxfId="21"/>
+    <tableColumn id="14" xr3:uid="{29E6C5DC-7EA4-49BD-9F29-57DA71718F20}" name="Área Responsable" dataDxfId="20"/>
+    <tableColumn id="15" xr3:uid="{2B6D1608-654F-4177-832E-561B75E0AA26}" name="Fecha Compromiso" dataDxfId="19"/>
+    <tableColumn id="16" xr3:uid="{1ED50EB0-1860-4E22-9EF1-F93210496EDD}" name="Evidencia Esperada" dataDxfId="18"/>
+    <tableColumn id="17" xr3:uid="{8F0EB8AC-437B-4325-8ABA-666909D9B5F8}" name="Indicador de Cumplimiento" dataDxfId="17"/>
+    <tableColumn id="18" xr3:uid="{C7EEC45E-ECAD-4B56-93C0-4B5AE924CD8E}" name="Estado Automático" dataDxfId="16"/>
+    <tableColumn id="19" xr3:uid="{2722D635-9314-4F49-B035-B9A724C5210A}" name="% Avance" dataDxfId="15"/>
+    <tableColumn id="20" xr3:uid="{28A730BA-4EA7-49DF-9399-6E00D5292AB2}" name="Fecha Último Seguimiento" dataDxfId="14"/>
+    <tableColumn id="21" xr3:uid="{F70EE4EC-D6C1-4265-B078-19D148BC2906}" name="Observaciones de Seguimiento" dataDxfId="13"/>
+    <tableColumn id="22" xr3:uid="{C964C47F-52C9-426B-B6E5-974094EDB9DE}" name="Escalado a Dirección" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{36A8271D-7EA2-487A-A00A-D3AD91C530B1}" name="Fecha de Escalamiento" dataDxfId="11"/>
+    <tableColumn id="24" xr3:uid="{AB72CFF0-E4FD-4906-9E3E-23B7E97C9D47}" name="Fecha Implementación Real" dataDxfId="10"/>
+    <tableColumn id="25" xr3:uid="{2E3BE42A-F44C-4E50-AF37-498FDB63B8C9}" name="Tipo de Validación" dataDxfId="9"/>
+    <tableColumn id="26" xr3:uid="{F12F1141-56CD-411F-8B57-54F18AE19AB1}" name="Resultado de Validación" dataDxfId="8"/>
+    <tableColumn id="27" xr3:uid="{B53A8C3D-2477-4D08-BBF6-39ED220F441F}" name="Auditor que Valida" dataDxfId="7"/>
+    <tableColumn id="28" xr3:uid="{02AE6B85-C8E3-458F-99DE-6C3A7C997538}" name="Fecha Cierre Oficial" dataDxfId="6"/>
+    <tableColumn id="29" xr3:uid="{0280F784-8789-4BD2-8B63-2885D043177E}" name="Reincidencia" dataDxfId="5"/>
+    <tableColumn id="30" xr3:uid="{B33911EB-ED81-48C2-8376-B92BC2D7744C}" name="Impacto Mitigado" dataDxfId="4"/>
+    <tableColumn id="31" xr3:uid="{8ACAEBDD-C331-4809-91C4-834E371130EB}" name="Comentarios de Cierre" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6492,13 +6492,13 @@
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Bajo">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Bajo">
       <formula>NOT(ISERROR(SEARCH("Bajo",G1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="Medio">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Medio">
       <formula>NOT(ISERROR(SEARCH("Medio",G1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="Alto">
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Alto">
       <formula>NOT(ISERROR(SEARCH("Alto",G1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/Matriz_Seguimiento_Hallazgos.xlsx
+++ b/data/Matriz_Seguimiento_Hallazgos.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="649" documentId="8_{B9D78422-FDFF-47F2-8818-479A70B2C122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4CD6886-50A6-40E3-A932-647951E02FB5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base Hallazgos SIG" sheetId="4" r:id="rId1"/>
@@ -1812,6 +1812,130 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1911,6 +2035,201 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1941,7 +2260,7 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1976,13 +2295,14 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -2023,247 +2343,6 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -3147,7 +3226,211 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -3195,6 +3478,171 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -3230,454 +3678,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -3783,81 +3783,81 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5BA7D11D-A526-4CEA-9DF8-80ED50D1CBD9}" name="Tabla3" displayName="Tabla3" ref="A1:AG13" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71" tableBorderDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5BA7D11D-A526-4CEA-9DF8-80ED50D1CBD9}" name="Tabla3" displayName="Tabla3" ref="A1:AG13" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37" tableBorderDxfId="36">
   <tableColumns count="33">
-    <tableColumn id="1" xr3:uid="{38023AA5-9776-4E80-A951-BE0FE68F1101}" name="Código Hallazgo" dataDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{883B5642-97A6-4B67-A91F-312BB25E116A}" name="Fecha de Detección" dataDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{C0E29A75-6D52-44C1-BBC8-1D0D9854730F}" name="Auditoría" dataDxfId="67"/>
-    <tableColumn id="4" xr3:uid="{F8A3A88E-425E-4914-B771-61B543B87499}" name="Proceso" dataDxfId="66"/>
-    <tableColumn id="5" xr3:uid="{4115E30F-D80C-45FD-BBCE-3C3D007A45F0}" name="Subproceso" dataDxfId="65"/>
-    <tableColumn id="6" xr3:uid="{D5E799E7-238C-4410-8180-2F23404C38C5}" name="Responsable del Proceso" dataDxfId="64"/>
-    <tableColumn id="7" xr3:uid="{EF5F4C2C-D1C7-44F0-A107-641607336071}" name="Criterio Incumplido" dataDxfId="63"/>
-    <tableColumn id="8" xr3:uid="{F98540B2-06C0-4AB3-A036-DA30F86A9127}" name="Descripción del Hallazgo" dataDxfId="62"/>
-    <tableColumn id="9" xr3:uid="{7488B0F2-484A-4D7A-806A-B20AD5A4B44B}" name="Evidencia" dataDxfId="61"/>
-    <tableColumn id="10" xr3:uid="{3046F0F7-5132-4A53-A672-1A0D51F6FD90}" name="Causa Raíz" dataDxfId="60"/>
-    <tableColumn id="11" xr3:uid="{51F65AE4-A931-4F03-9144-11BB7E1BA7EC}" name="Riesgos Asociados" dataDxfId="59"/>
-    <tableColumn id="12" xr3:uid="{DEAD9D0A-B936-416F-A091-B28F8DC890CA}" name="Tipo de Acción" dataDxfId="58"/>
-    <tableColumn id="13" xr3:uid="{8C244D88-600C-4C82-BC90-B9A59CFC691C}" name="Acción Correctiva" dataDxfId="57"/>
-    <tableColumn id="14" xr3:uid="{DE25F41D-7D67-47E8-BB59-37A2E153EEB2}" name="Avance" dataDxfId="56"/>
-    <tableColumn id="15" xr3:uid="{97EE2963-728C-4A52-A616-D5ABCB743209}" name="Responsable de la Acción" dataDxfId="55"/>
-    <tableColumn id="16" xr3:uid="{093911F5-09A4-453E-8292-E386A79C9C1D}" name="Área Responsable" dataDxfId="54"/>
-    <tableColumn id="17" xr3:uid="{DD857392-716E-4350-AE9B-2A43A13A5903}" name="Fecha Compromiso" dataDxfId="53"/>
-    <tableColumn id="18" xr3:uid="{1F28FB8B-3090-4702-AC1B-D1B5EA0CA13F}" name="Evidencia Esperada" dataDxfId="52"/>
-    <tableColumn id="19" xr3:uid="{D64795B7-F5AF-4717-BF92-0B8A45C7B89C}" name="Indicador de Cumplimiento" dataDxfId="51"/>
-    <tableColumn id="20" xr3:uid="{9280B508-D669-4CE9-A7D9-2F6D29B1724B}" name="Estado Automático" dataDxfId="50"/>
-    <tableColumn id="21" xr3:uid="{A6E3D81D-F7AE-4126-BAC2-068953DF2A77}" name="% Avance" dataDxfId="49"/>
-    <tableColumn id="22" xr3:uid="{83E6ABB0-426C-477B-901F-15705ACCE8EA}" name="Fecha Último Seguimiento" dataDxfId="48"/>
-    <tableColumn id="23" xr3:uid="{F01F5465-D84D-4303-B442-EEF87F5FE407}" name="Observaciones de Seguimiento" dataDxfId="47"/>
-    <tableColumn id="24" xr3:uid="{FD269743-574B-4863-B455-390ACA96A5DE}" name="Escalado a Dirección" dataDxfId="46"/>
-    <tableColumn id="25" xr3:uid="{2E7ACEE0-5BD8-4436-B3AE-0157D22A3C8B}" name="Fecha de Escalamiento" dataDxfId="45"/>
-    <tableColumn id="26" xr3:uid="{61668FD7-E523-4D93-8EF7-63F3BCC15C61}" name="Fecha Implementación Real" dataDxfId="44"/>
-    <tableColumn id="27" xr3:uid="{40ABE0DD-161B-40D2-BC22-91747FB660E9}" name="Tipo de Validación" dataDxfId="43"/>
-    <tableColumn id="28" xr3:uid="{63735BCB-A0AD-4E66-B6EF-82CD0E5C8017}" name="Resultado de Validación" dataDxfId="42"/>
-    <tableColumn id="29" xr3:uid="{D137839B-0857-4CB3-B34D-0F30B28A8620}" name="Auditor que Valida" dataDxfId="41"/>
-    <tableColumn id="30" xr3:uid="{31624A5B-76AA-4C9E-8DF7-1BE589EC1D2B}" name="Fecha Cierre Oficial" dataDxfId="40"/>
-    <tableColumn id="31" xr3:uid="{21402088-000E-4EE6-B3CF-1172741519CA}" name="Reincidencia" dataDxfId="39"/>
-    <tableColumn id="32" xr3:uid="{7D71CFD1-9D53-4496-A1F8-E2B7ED050B67}" name="Impacto Mitigado" dataDxfId="38"/>
-    <tableColumn id="33" xr3:uid="{30C54FB7-6AE1-410A-B899-BC22AC520A10}" name="Comentarios de Cierre" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{38023AA5-9776-4E80-A951-BE0FE68F1101}" name="Código Hallazgo" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{883B5642-97A6-4B67-A91F-312BB25E116A}" name="Fecha de Detección" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{C0E29A75-6D52-44C1-BBC8-1D0D9854730F}" name="Auditoría" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{F8A3A88E-425E-4914-B771-61B543B87499}" name="Proceso" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{4115E30F-D80C-45FD-BBCE-3C3D007A45F0}" name="Subproceso" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{D5E799E7-238C-4410-8180-2F23404C38C5}" name="Responsable del Proceso" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{EF5F4C2C-D1C7-44F0-A107-641607336071}" name="Criterio Incumplido" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{F98540B2-06C0-4AB3-A036-DA30F86A9127}" name="Descripción del Hallazgo" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{7488B0F2-484A-4D7A-806A-B20AD5A4B44B}" name="Evidencia" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{3046F0F7-5132-4A53-A672-1A0D51F6FD90}" name="Causa Raíz" dataDxfId="26"/>
+    <tableColumn id="11" xr3:uid="{51F65AE4-A931-4F03-9144-11BB7E1BA7EC}" name="Riesgos Asociados" dataDxfId="25"/>
+    <tableColumn id="12" xr3:uid="{DEAD9D0A-B936-416F-A091-B28F8DC890CA}" name="Tipo de Acción" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{8C244D88-600C-4C82-BC90-B9A59CFC691C}" name="Acción Correctiva" dataDxfId="23"/>
+    <tableColumn id="14" xr3:uid="{DE25F41D-7D67-47E8-BB59-37A2E153EEB2}" name="Avance" dataDxfId="22"/>
+    <tableColumn id="15" xr3:uid="{97EE2963-728C-4A52-A616-D5ABCB743209}" name="Responsable de la Acción" dataDxfId="21"/>
+    <tableColumn id="16" xr3:uid="{093911F5-09A4-453E-8292-E386A79C9C1D}" name="Área Responsable" dataDxfId="20"/>
+    <tableColumn id="17" xr3:uid="{DD857392-716E-4350-AE9B-2A43A13A5903}" name="Fecha Compromiso" dataDxfId="19"/>
+    <tableColumn id="18" xr3:uid="{1F28FB8B-3090-4702-AC1B-D1B5EA0CA13F}" name="Evidencia Esperada" dataDxfId="18"/>
+    <tableColumn id="19" xr3:uid="{D64795B7-F5AF-4717-BF92-0B8A45C7B89C}" name="Indicador de Cumplimiento" dataDxfId="17"/>
+    <tableColumn id="20" xr3:uid="{9280B508-D669-4CE9-A7D9-2F6D29B1724B}" name="Estado Automático" dataDxfId="16"/>
+    <tableColumn id="21" xr3:uid="{A6E3D81D-F7AE-4126-BAC2-068953DF2A77}" name="% Avance" dataDxfId="15"/>
+    <tableColumn id="22" xr3:uid="{83E6ABB0-426C-477B-901F-15705ACCE8EA}" name="Fecha Último Seguimiento" dataDxfId="14"/>
+    <tableColumn id="23" xr3:uid="{F01F5465-D84D-4303-B442-EEF87F5FE407}" name="Observaciones de Seguimiento" dataDxfId="13"/>
+    <tableColumn id="24" xr3:uid="{FD269743-574B-4863-B455-390ACA96A5DE}" name="Escalado a Dirección" dataDxfId="12"/>
+    <tableColumn id="25" xr3:uid="{2E7ACEE0-5BD8-4436-B3AE-0157D22A3C8B}" name="Fecha de Escalamiento" dataDxfId="11"/>
+    <tableColumn id="26" xr3:uid="{61668FD7-E523-4D93-8EF7-63F3BCC15C61}" name="Fecha Implementación Real" dataDxfId="10"/>
+    <tableColumn id="27" xr3:uid="{40ABE0DD-161B-40D2-BC22-91747FB660E9}" name="Tipo de Validación" dataDxfId="9"/>
+    <tableColumn id="28" xr3:uid="{63735BCB-A0AD-4E66-B6EF-82CD0E5C8017}" name="Resultado de Validación" dataDxfId="8"/>
+    <tableColumn id="29" xr3:uid="{D137839B-0857-4CB3-B34D-0F30B28A8620}" name="Auditor que Valida" dataDxfId="7"/>
+    <tableColumn id="30" xr3:uid="{31624A5B-76AA-4C9E-8DF7-1BE589EC1D2B}" name="Fecha Cierre Oficial" dataDxfId="6"/>
+    <tableColumn id="31" xr3:uid="{21402088-000E-4EE6-B3CF-1172741519CA}" name="Reincidencia" dataDxfId="5"/>
+    <tableColumn id="32" xr3:uid="{7D71CFD1-9D53-4496-A1F8-E2B7ED050B67}" name="Impacto Mitigado" dataDxfId="4"/>
+    <tableColumn id="33" xr3:uid="{30C54FB7-6AE1-410A-B899-BC22AC520A10}" name="Comentarios de Cierre" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{22FB0005-8F63-4CE1-938E-B216418660F6}" name="Tabla1" displayName="Tabla1" ref="A1:AE25" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35" tableBorderDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{22FB0005-8F63-4CE1-938E-B216418660F6}" name="Tabla1" displayName="Tabla1" ref="A1:AE25" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71" tableBorderDxfId="70">
   <autoFilter ref="A1:AE25" xr:uid="{22FB0005-8F63-4CE1-938E-B216418660F6}"/>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{C445E1C6-F781-4A05-A8DB-BB9CC1F5A338}" name="Código Hallazgo" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{90EAE778-D38B-49EF-B34D-315F9A7A5A27}" name="Fecha de Cierre" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{C0D5052E-084A-4422-8247-58D55C619725}" name="Auditoría" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{5D3256A2-BA02-44EC-95EB-2C06CE880405}" name="Proceso" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{893633F6-D257-4D10-8927-3D3A728B911A}" name="Subproceso" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{1ACBDFC4-A8D2-4E4E-B0A8-F320C769D36F}" name="Responsable del Proceso" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{458512AC-6A36-47C9-AC84-D62D31450CAA}" name="Criticidad" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{F2E3079A-A9A6-49A5-A02F-AF83100B696B}" name="Criterio Incumplido" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{42F33B5C-BC64-4551-83E2-5C33C69EC227}" name="Descripción del Hallazgo" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{9CF403EB-8414-4F4C-B74F-0679F4979A1C}" name="Riesgos Asociados" dataDxfId="24"/>
-    <tableColumn id="11" xr3:uid="{F4506974-B5EF-4B33-A978-8D4F503123A7}" name="Tipo de Acción" dataDxfId="23"/>
-    <tableColumn id="12" xr3:uid="{2A3BC71B-97A7-4F6A-A427-E20FA980B65F}" name="Acciones / Actividades" dataDxfId="22"/>
-    <tableColumn id="13" xr3:uid="{2CDD1D9D-33E2-44C4-94C7-280236B55BA8}" name="Responsable de la Acción" dataDxfId="21"/>
-    <tableColumn id="14" xr3:uid="{29E6C5DC-7EA4-49BD-9F29-57DA71718F20}" name="Área Responsable" dataDxfId="20"/>
-    <tableColumn id="15" xr3:uid="{2B6D1608-654F-4177-832E-561B75E0AA26}" name="Fecha Compromiso" dataDxfId="19"/>
-    <tableColumn id="16" xr3:uid="{1ED50EB0-1860-4E22-9EF1-F93210496EDD}" name="Evidencia Esperada" dataDxfId="18"/>
-    <tableColumn id="17" xr3:uid="{8F0EB8AC-437B-4325-8ABA-666909D9B5F8}" name="Indicador de Cumplimiento" dataDxfId="17"/>
-    <tableColumn id="18" xr3:uid="{C7EEC45E-ECAD-4B56-93C0-4B5AE924CD8E}" name="Estado Automático" dataDxfId="16"/>
-    <tableColumn id="19" xr3:uid="{2722D635-9314-4F49-B035-B9A724C5210A}" name="% Avance" dataDxfId="15"/>
-    <tableColumn id="20" xr3:uid="{28A730BA-4EA7-49DF-9399-6E00D5292AB2}" name="Fecha Último Seguimiento" dataDxfId="14"/>
-    <tableColumn id="21" xr3:uid="{F70EE4EC-D6C1-4265-B078-19D148BC2906}" name="Observaciones de Seguimiento" dataDxfId="13"/>
-    <tableColumn id="22" xr3:uid="{C964C47F-52C9-426B-B6E5-974094EDB9DE}" name="Escalado a Dirección" dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{36A8271D-7EA2-487A-A00A-D3AD91C530B1}" name="Fecha de Escalamiento" dataDxfId="11"/>
-    <tableColumn id="24" xr3:uid="{AB72CFF0-E4FD-4906-9E3E-23B7E97C9D47}" name="Fecha Implementación Real" dataDxfId="10"/>
-    <tableColumn id="25" xr3:uid="{2E3BE42A-F44C-4E50-AF37-498FDB63B8C9}" name="Tipo de Validación" dataDxfId="9"/>
-    <tableColumn id="26" xr3:uid="{F12F1141-56CD-411F-8B57-54F18AE19AB1}" name="Resultado de Validación" dataDxfId="8"/>
-    <tableColumn id="27" xr3:uid="{B53A8C3D-2477-4D08-BBF6-39ED220F441F}" name="Auditor que Valida" dataDxfId="7"/>
-    <tableColumn id="28" xr3:uid="{02AE6B85-C8E3-458F-99DE-6C3A7C997538}" name="Fecha Cierre Oficial" dataDxfId="6"/>
-    <tableColumn id="29" xr3:uid="{0280F784-8789-4BD2-8B63-2885D043177E}" name="Reincidencia" dataDxfId="5"/>
-    <tableColumn id="30" xr3:uid="{B33911EB-ED81-48C2-8376-B92BC2D7744C}" name="Impacto Mitigado" dataDxfId="4"/>
-    <tableColumn id="31" xr3:uid="{8ACAEBDD-C331-4809-91C4-834E371130EB}" name="Comentarios de Cierre" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{C445E1C6-F781-4A05-A8DB-BB9CC1F5A338}" name="Código Hallazgo" dataDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{90EAE778-D38B-49EF-B34D-315F9A7A5A27}" name="Fecha de Cierre" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{C0D5052E-084A-4422-8247-58D55C619725}" name="Auditoría" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{5D3256A2-BA02-44EC-95EB-2C06CE880405}" name="Proceso" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{893633F6-D257-4D10-8927-3D3A728B911A}" name="Subproceso" dataDxfId="65"/>
+    <tableColumn id="6" xr3:uid="{1ACBDFC4-A8D2-4E4E-B0A8-F320C769D36F}" name="Responsable del Proceso" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{458512AC-6A36-47C9-AC84-D62D31450CAA}" name="Criticidad" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{F2E3079A-A9A6-49A5-A02F-AF83100B696B}" name="Criterio Incumplido" dataDxfId="62"/>
+    <tableColumn id="9" xr3:uid="{42F33B5C-BC64-4551-83E2-5C33C69EC227}" name="Descripción del Hallazgo" dataDxfId="61"/>
+    <tableColumn id="10" xr3:uid="{9CF403EB-8414-4F4C-B74F-0679F4979A1C}" name="Riesgos Asociados" dataDxfId="60"/>
+    <tableColumn id="11" xr3:uid="{F4506974-B5EF-4B33-A978-8D4F503123A7}" name="Tipo de Acción" dataDxfId="59"/>
+    <tableColumn id="12" xr3:uid="{2A3BC71B-97A7-4F6A-A427-E20FA980B65F}" name="Acciones / Actividades" dataDxfId="58"/>
+    <tableColumn id="13" xr3:uid="{2CDD1D9D-33E2-44C4-94C7-280236B55BA8}" name="Responsable de la Acción" dataDxfId="57"/>
+    <tableColumn id="14" xr3:uid="{29E6C5DC-7EA4-49BD-9F29-57DA71718F20}" name="Área Responsable" dataDxfId="56"/>
+    <tableColumn id="15" xr3:uid="{2B6D1608-654F-4177-832E-561B75E0AA26}" name="Fecha Compromiso" dataDxfId="55"/>
+    <tableColumn id="16" xr3:uid="{1ED50EB0-1860-4E22-9EF1-F93210496EDD}" name="Evidencia Esperada" dataDxfId="54"/>
+    <tableColumn id="17" xr3:uid="{8F0EB8AC-437B-4325-8ABA-666909D9B5F8}" name="Indicador de Cumplimiento" dataDxfId="53"/>
+    <tableColumn id="18" xr3:uid="{C7EEC45E-ECAD-4B56-93C0-4B5AE924CD8E}" name="Estado Automático" dataDxfId="52"/>
+    <tableColumn id="19" xr3:uid="{2722D635-9314-4F49-B035-B9A724C5210A}" name="% Avance" dataDxfId="51"/>
+    <tableColumn id="20" xr3:uid="{28A730BA-4EA7-49DF-9399-6E00D5292AB2}" name="Fecha Último Seguimiento" dataDxfId="50"/>
+    <tableColumn id="21" xr3:uid="{F70EE4EC-D6C1-4265-B078-19D148BC2906}" name="Observaciones de Seguimiento" dataDxfId="49"/>
+    <tableColumn id="22" xr3:uid="{C964C47F-52C9-426B-B6E5-974094EDB9DE}" name="Escalado a Dirección" dataDxfId="48"/>
+    <tableColumn id="23" xr3:uid="{36A8271D-7EA2-487A-A00A-D3AD91C530B1}" name="Fecha de Escalamiento" dataDxfId="47"/>
+    <tableColumn id="24" xr3:uid="{AB72CFF0-E4FD-4906-9E3E-23B7E97C9D47}" name="Fecha Implementación Real" dataDxfId="46"/>
+    <tableColumn id="25" xr3:uid="{2E3BE42A-F44C-4E50-AF37-498FDB63B8C9}" name="Tipo de Validación" dataDxfId="45"/>
+    <tableColumn id="26" xr3:uid="{F12F1141-56CD-411F-8B57-54F18AE19AB1}" name="Resultado de Validación" dataDxfId="44"/>
+    <tableColumn id="27" xr3:uid="{B53A8C3D-2477-4D08-BBF6-39ED220F441F}" name="Auditor que Valida" dataDxfId="43"/>
+    <tableColumn id="28" xr3:uid="{02AE6B85-C8E3-458F-99DE-6C3A7C997538}" name="Fecha Cierre Oficial" dataDxfId="42"/>
+    <tableColumn id="29" xr3:uid="{0280F784-8789-4BD2-8B63-2885D043177E}" name="Reincidencia" dataDxfId="41"/>
+    <tableColumn id="30" xr3:uid="{B33911EB-ED81-48C2-8376-B92BC2D7744C}" name="Impacto Mitigado" dataDxfId="40"/>
+    <tableColumn id="31" xr3:uid="{8ACAEBDD-C331-4809-91C4-834E371130EB}" name="Comentarios de Cierre" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5001,7 +5001,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="4">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="AB2:AB13" xr:uid="{274A9DB5-4743-4598-9019-2B28638E96CF}">
       <formula1>"Eficaz,Parcialmente eficaz,No eficaz"</formula1>
     </dataValidation>
